--- a/URUVS/Datasheets/URUV/05.2024/May_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/05.2024/May_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sophi\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\05.2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\05.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5C8EF8-E944-4AFB-81D5-1FCD9FF5B497}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC2894B-121B-4353-8FFE-D12B5BC313EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RecordingData_05.2024" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Metadata" sheetId="6" r:id="rId3"/>
     <sheet name="LATLON" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,6 +26,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="211">
   <si>
     <t>DATE</t>
   </si>
@@ -639,6 +645,33 @@
   </si>
   <si>
     <t>MAY</t>
+  </si>
+  <si>
+    <t>MAXN_MUDCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STMUDCRAB</t>
+  </si>
+  <si>
+    <t>T1_MUDCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STSWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>T1_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SHRIMP</t>
+  </si>
+  <si>
+    <t>TIME_SHRIMP</t>
+  </si>
+  <si>
+    <t>T1_SHRIMP</t>
   </si>
 </sst>
 </file>
@@ -879,15 +912,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
@@ -900,8 +933,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -912,28 +945,27 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="21" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -942,10 +974,10 @@
     <xf numFmtId="46" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -957,11 +989,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
@@ -975,26 +1007,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="21" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="21" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -1277,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:DF19"/>
+  <dimension ref="A1:DO19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -1292,7 +1319,6 @@
     <col min="52" max="52" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="8.7265625" style="71"/>
     <col min="79" max="79" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="85" max="85" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="88" max="88" width="18.36328125" bestFit="1" customWidth="1"/>
@@ -1300,10 +1326,13 @@
     <col min="103" max="103" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="106" max="106" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:110" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:119" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>200</v>
       </c>
@@ -1319,7 +1348,7 @@
       <c r="E1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="73" t="s">
+      <c r="F1" s="71" t="s">
         <v>98</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -1412,230 +1441,257 @@
       <c r="AJ1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="AK1" s="58" t="s">
+      <c r="AK1" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="AL1" s="81" t="s">
+      <c r="AL1" s="79" t="s">
         <v>48</v>
       </c>
       <c r="AM1" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="AN1" s="58" t="s">
+      <c r="AN1" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="AO1" s="81" t="s">
+      <c r="AO1" s="79" t="s">
         <v>55</v>
       </c>
       <c r="AP1" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="AQ1" s="58" t="s">
+      <c r="AQ1" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="AR1" s="81" t="s">
+      <c r="AR1" s="79" t="s">
         <v>39</v>
       </c>
       <c r="AS1" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="AT1" s="58" t="s">
+      <c r="AT1" s="57" t="s">
         <v>41</v>
       </c>
-      <c r="AU1" s="81" t="s">
+      <c r="AU1" s="79" t="s">
         <v>52</v>
       </c>
       <c r="AV1" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="AW1" s="58" t="s">
+      <c r="AW1" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="AX1" s="81" t="s">
+      <c r="AX1" s="79" t="s">
         <v>129</v>
       </c>
       <c r="AY1" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="AZ1" s="58" t="s">
+      <c r="AZ1" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="BA1" s="81" t="s">
+      <c r="BA1" s="79" t="s">
         <v>36</v>
       </c>
       <c r="BB1" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="BC1" s="58" t="s">
+      <c r="BC1" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="BD1" s="81" t="s">
+      <c r="BD1" s="79" t="s">
         <v>45</v>
       </c>
       <c r="BE1" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="BF1" s="58" t="s">
+      <c r="BF1" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="BG1" s="81" t="s">
+      <c r="BG1" s="79" t="s">
         <v>42</v>
       </c>
       <c r="BH1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="BI1" s="58" t="s">
+      <c r="BI1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="BJ1" s="81" t="s">
+      <c r="BJ1" s="79" t="s">
         <v>50</v>
       </c>
       <c r="BK1" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="BL1" s="58" t="s">
+      <c r="BL1" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="BM1" s="81" t="s">
+      <c r="BM1" s="79" t="s">
         <v>59</v>
       </c>
       <c r="BN1" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="BO1" s="58" t="s">
+      <c r="BO1" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="BP1" s="81" t="s">
+      <c r="BP1" s="79" t="s">
         <v>62</v>
       </c>
       <c r="BQ1" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="BR1" s="58" t="s">
+      <c r="BR1" s="57" t="s">
         <v>64</v>
       </c>
-      <c r="BS1" s="81" t="s">
+      <c r="BS1" s="79" t="s">
         <v>117</v>
       </c>
       <c r="BT1" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="BU1" s="58" t="s">
+      <c r="BU1" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="BV1" s="81" t="s">
+      <c r="BV1" s="79" t="s">
         <v>120</v>
       </c>
       <c r="BW1" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="BX1" s="58" t="s">
+      <c r="BX1" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="BY1" s="82" t="s">
+      <c r="BY1" s="79" t="s">
         <v>126</v>
       </c>
       <c r="BZ1" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="CA1" s="58" t="s">
+      <c r="CA1" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="CB1" s="81" t="s">
+      <c r="CB1" s="79" t="s">
         <v>138</v>
       </c>
       <c r="CC1" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="CD1" s="58" t="s">
+      <c r="CD1" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="CE1" s="81" t="s">
+      <c r="CE1" s="79" t="s">
         <v>197</v>
       </c>
       <c r="CF1" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="CG1" s="58" t="s">
+      <c r="CG1" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="CH1" s="81" t="s">
+      <c r="CH1" s="79" t="s">
         <v>123</v>
       </c>
       <c r="CI1" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="CJ1" s="58" t="s">
+      <c r="CJ1" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="CK1" s="81" t="s">
+      <c r="CK1" s="79" t="s">
         <v>132</v>
       </c>
       <c r="CL1" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="CM1" s="58" t="s">
+      <c r="CM1" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="CN1" s="81" t="s">
+      <c r="CN1" s="79" t="s">
         <v>135</v>
       </c>
       <c r="CO1" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="CP1" s="58" t="s">
+      <c r="CP1" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="CQ1" s="81" t="s">
+      <c r="CQ1" s="79" t="s">
         <v>65</v>
       </c>
       <c r="CR1" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="CS1" s="58" t="s">
+      <c r="CS1" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="CT1" s="81" t="s">
+      <c r="CT1" s="79" t="s">
         <v>189</v>
       </c>
       <c r="CU1" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="CV1" s="58" t="s">
+      <c r="CV1" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="CW1" s="81" t="s">
+      <c r="CW1" s="79" t="s">
         <v>141</v>
       </c>
       <c r="CX1" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="CY1" s="58" t="s">
+      <c r="CY1" s="57" t="s">
         <v>143</v>
       </c>
-      <c r="CZ1" s="81" t="s">
+      <c r="CZ1" s="79" t="s">
         <v>192</v>
       </c>
       <c r="DA1" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="DB1" s="58" t="s">
+      <c r="DB1" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="DC1" s="81" t="s">
+      <c r="DC1" s="79" t="s">
         <v>12</v>
       </c>
       <c r="DD1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="DE1" s="58" t="s">
+      <c r="DE1" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="DF1" s="28" t="s">
+      <c r="DF1" s="79" t="s">
+        <v>202</v>
+      </c>
+      <c r="DG1" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="DH1" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="DI1" s="79" t="s">
+        <v>205</v>
+      </c>
+      <c r="DJ1" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="DK1" s="57" t="s">
+        <v>207</v>
+      </c>
+      <c r="DL1" s="79" t="s">
+        <v>208</v>
+      </c>
+      <c r="DM1" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="DN1" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="DO1" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>201</v>
       </c>
@@ -1651,7 +1707,7 @@
       <c r="E2" s="5">
         <v>2</v>
       </c>
-      <c r="F2" s="74" t="str">
+      <c r="F2" s="72" t="str">
         <f>D2&amp;""&amp;E2</f>
         <v>D2</v>
       </c>
@@ -1740,10 +1796,10 @@
       </c>
       <c r="AI2" s="22"/>
       <c r="AJ2" s="29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK2" s="30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL2" s="31"/>
       <c r="AM2" s="34"/>
@@ -1751,175 +1807,197 @@
         <f t="shared" ref="AN2:AN13" si="1">IF(AL2=0,"NA",AM2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="AO2" s="57">
+      <c r="AO2" s="56">
         <v>1</v>
       </c>
-      <c r="AP2" s="70">
+      <c r="AP2" s="69">
         <v>3.9467592592592596E-2</v>
       </c>
       <c r="AQ2" s="33">
         <f t="shared" ref="AQ2:AQ13" si="2">IF(AO2=0,"NA",AP2-$AD2)</f>
         <v>3.5659722222222225E-2</v>
       </c>
-      <c r="AR2" s="57"/>
-      <c r="AS2" s="56"/>
+      <c r="AR2" s="56"/>
+      <c r="AS2" s="55"/>
       <c r="AT2" s="33" t="str">
         <f t="shared" ref="AT2:AT13" si="3">IF(AR2=0,"NA",AS2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="AU2" s="57"/>
-      <c r="AV2" s="56"/>
+      <c r="AU2" s="56"/>
+      <c r="AV2" s="55"/>
       <c r="AW2" s="33" t="str">
         <f t="shared" ref="AW2:AW13" si="4">IF(AU2=0,"NA",AV2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="AX2" s="57"/>
-      <c r="AY2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="55"/>
       <c r="AZ2" s="33" t="str">
         <f t="shared" ref="AZ2:AZ19" si="5">IF(AX2=0,"NA",AY2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BA2" s="57"/>
-      <c r="BB2" s="70"/>
+      <c r="BA2" s="56"/>
+      <c r="BB2" s="69"/>
       <c r="BC2" s="33" t="str">
         <f t="shared" ref="BC2:BC13" si="6">IF(BA2=0,"NA",BB2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BD2" s="57"/>
-      <c r="BE2" s="56"/>
+      <c r="BD2" s="56"/>
+      <c r="BE2" s="55"/>
       <c r="BF2" s="33" t="str">
         <f t="shared" ref="BF2:BF13" si="7">IF(BD2=0,"NA",BE2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BG2" s="57"/>
-      <c r="BH2" s="56"/>
+      <c r="BG2" s="56"/>
+      <c r="BH2" s="55"/>
       <c r="BI2" s="33" t="str">
         <f t="shared" ref="BI2:BI13" si="8">IF(BG2=0,"NA",BH2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BJ2" s="57">
+      <c r="BJ2" s="56">
         <v>2</v>
       </c>
-      <c r="BK2" s="70">
+      <c r="BK2" s="69">
         <v>9.0277777777777787E-3</v>
       </c>
       <c r="BL2" s="33">
         <f t="shared" ref="BL2:BL13" si="9">IF(BJ2=0,"NA",BK2-$AD2)</f>
         <v>5.2199074074074075E-3</v>
       </c>
-      <c r="BM2" s="57"/>
-      <c r="BN2" s="56"/>
+      <c r="BM2" s="56"/>
+      <c r="BN2" s="55"/>
       <c r="BO2" s="33" t="str">
         <f t="shared" ref="BO2:BO13" si="10">IF(BM2=0,"NA",BN2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BP2" s="57"/>
-      <c r="BQ2" s="56"/>
+      <c r="BP2" s="56"/>
+      <c r="BQ2" s="55"/>
       <c r="BR2" s="33" t="str">
         <f t="shared" ref="BR2:BR13" si="11">IF(BP2=0,"NA",BQ2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BS2" s="57">
+      <c r="BS2" s="56">
         <v>3</v>
       </c>
-      <c r="BT2" s="72">
-        <v>1.8032407407407407E-2</v>
+      <c r="BT2" s="70">
+        <v>1.4513888888888889E-2</v>
       </c>
       <c r="BU2" s="33">
         <f t="shared" ref="BU2:BU13" si="12">IF(BS2=0,"NA",BT2-$AD2)</f>
-        <v>1.4224537037037036E-2</v>
-      </c>
-      <c r="BV2" s="57"/>
-      <c r="BW2" s="56"/>
+        <v>1.0706018518518517E-2</v>
+      </c>
+      <c r="BV2" s="56"/>
+      <c r="BW2" s="55"/>
       <c r="BX2" s="33" t="str">
         <f t="shared" ref="BX2:BX19" si="13">IF(BV2=0,"NA",BW2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BY2" s="40"/>
-      <c r="BZ2" s="55"/>
+      <c r="BY2" s="31"/>
+      <c r="BZ2" s="54"/>
       <c r="CA2" s="33" t="str">
         <f t="shared" ref="CA2:CA19" si="14">IF(BY2=0,"NA",BZ2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CB2" s="57">
+      <c r="CB2" s="56">
         <v>3</v>
       </c>
-      <c r="CC2" s="70">
+      <c r="CC2" s="69">
         <v>3.8425925925925923E-3</v>
       </c>
       <c r="CD2" s="33">
         <f t="shared" ref="CD2:CD19" si="15">IF(CB2=0,"NA",CC2-$AD2)</f>
         <v>3.4722222222221578E-5</v>
       </c>
-      <c r="CE2" s="57">
+      <c r="CE2" s="56">
         <v>1</v>
       </c>
-      <c r="CF2" s="70">
+      <c r="CF2" s="69">
         <v>3.7222222222222219E-2</v>
       </c>
       <c r="CG2" s="33">
         <f t="shared" ref="CG2:CG19" si="16">IF(CE2=0,"NA",CF2-$AD2)</f>
         <v>3.3414351851851848E-2</v>
       </c>
-      <c r="CH2" s="57">
+      <c r="CH2" s="56">
         <v>1</v>
       </c>
-      <c r="CI2" s="70">
-        <v>3.2615740740740744E-2</v>
+      <c r="CI2" s="69">
+        <v>1.9479166666666665E-2</v>
       </c>
       <c r="CJ2" s="33">
         <f t="shared" ref="CJ2:CJ19" si="17">IF(CH2=0,"NA",CI2-$AD2)</f>
-        <v>2.8807870370370373E-2</v>
-      </c>
-      <c r="CK2" s="57"/>
-      <c r="CL2" s="70"/>
+        <v>1.5671296296296294E-2</v>
+      </c>
+      <c r="CK2" s="56"/>
+      <c r="CL2" s="69"/>
       <c r="CM2" s="33" t="str">
         <f t="shared" ref="CM2:CM19" si="18">IF(CK2=0,"NA",CL2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CN2" s="57"/>
-      <c r="CO2" s="70"/>
+      <c r="CN2" s="56"/>
+      <c r="CO2" s="69"/>
       <c r="CP2" s="33" t="str">
         <f t="shared" ref="CP2:CP19" si="19">IF(CN2=0,"NA",CO2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CQ2" s="57"/>
-      <c r="CR2" s="70"/>
+      <c r="CQ2" s="56"/>
+      <c r="CR2" s="69"/>
       <c r="CS2" s="33" t="str">
         <f t="shared" ref="CS2:CS19" si="20">IF(CQ2=0,"NA",CR2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CT2" s="57">
+      <c r="CT2" s="56">
         <v>1</v>
       </c>
-      <c r="CU2" s="70">
+      <c r="CU2" s="69">
         <v>6.4814814814814813E-3</v>
       </c>
       <c r="CV2" s="33">
         <f t="shared" ref="CV2:CV19" si="21">IF(CT2=0,"NA",CU2-$AD2)</f>
         <v>2.6736111111111105E-3</v>
       </c>
-      <c r="CW2" s="57"/>
-      <c r="CX2" s="70"/>
+      <c r="CW2" s="56"/>
+      <c r="CX2" s="69"/>
       <c r="CY2" s="33" t="str">
         <f t="shared" ref="CY2:CY19" si="22">IF(CW2=0,"NA",CX2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="CZ2" s="57"/>
-      <c r="DA2" s="70"/>
+      <c r="CZ2" s="56"/>
+      <c r="DA2" s="69"/>
       <c r="DB2" s="33" t="str">
         <f t="shared" ref="DB2:DB19" si="23">IF(CZ2=0,"NA",DA2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="DC2" s="57"/>
-      <c r="DD2" s="70"/>
+      <c r="DC2" s="56"/>
+      <c r="DD2" s="69"/>
       <c r="DE2" s="33" t="str">
-        <f t="shared" ref="DE2:DE13" si="24">IF(DC2=0,"NA",DD2-$AD2)</f>
-        <v>NA</v>
-      </c>
-      <c r="DF2" s="35"/>
+        <f t="shared" ref="DE2:DE19" si="24">IF(DC2=0,"NA",DD2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DF2" s="56">
+        <v>1</v>
+      </c>
+      <c r="DG2" s="69">
+        <v>4.8148148148148152E-3</v>
+      </c>
+      <c r="DH2" s="33">
+        <f t="shared" ref="DH2:DH19" si="25">IF(DF2=0,"NA",DG2-$AD2)</f>
+        <v>1.0069444444444444E-3</v>
+      </c>
+      <c r="DI2" s="56"/>
+      <c r="DJ2" s="69"/>
+      <c r="DK2" s="33" t="str">
+        <f t="shared" ref="DK2:DK19" si="26">IF(DI2=0,"NA",DJ2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DL2" s="56"/>
+      <c r="DM2" s="69"/>
+      <c r="DN2" s="33" t="str">
+        <f t="shared" ref="DN2:DN13" si="27">IF(DL2=0,"NA",DM2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DO2" s="35"/>
     </row>
-    <row r="3" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>201</v>
       </c>
@@ -1935,8 +2013,8 @@
       <c r="E3" s="5">
         <v>1</v>
       </c>
-      <c r="F3" s="74" t="str">
-        <f t="shared" ref="F3:F19" si="25">D3&amp;""&amp;E3</f>
+      <c r="F3" s="72" t="str">
+        <f t="shared" ref="F3:F19" si="28">D3&amp;""&amp;E3</f>
         <v>E1</v>
       </c>
       <c r="G3" s="5">
@@ -1972,7 +2050,7 @@
         <v>3</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q19" si="26">J3-I3</f>
+        <f t="shared" ref="Q3:Q19" si="29">J3-I3</f>
         <v>7.3611111111111183E-2</v>
       </c>
       <c r="R3" s="6" t="s">
@@ -2001,7 +2079,7 @@
       <c r="AA3" s="20"/>
       <c r="AB3" s="20"/>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC19" si="27">SUM(W3:AB3)</f>
+        <f t="shared" ref="AC3:AC19" si="30">SUM(W3:AB3)</f>
         <v>4.5821759259259257E-2</v>
       </c>
       <c r="AD3" s="20">
@@ -2020,10 +2098,10 @@
       </c>
       <c r="AI3" s="22"/>
       <c r="AJ3" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK3" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL3" s="31">
         <v>44</v>
@@ -2115,8 +2193,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY3" s="40"/>
-      <c r="BZ3" s="55"/>
+      <c r="BY3" s="31"/>
+      <c r="BZ3" s="54"/>
       <c r="CA3" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -2185,9 +2263,27 @@
         <f t="shared" si="24"/>
         <v>7.0023148148148162E-3</v>
       </c>
-      <c r="DF3" s="35"/>
+      <c r="DF3" s="31"/>
+      <c r="DG3" s="32"/>
+      <c r="DH3" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI3" s="31"/>
+      <c r="DJ3" s="34"/>
+      <c r="DK3" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL3" s="31"/>
+      <c r="DM3" s="34"/>
+      <c r="DN3" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO3" s="35"/>
     </row>
-    <row r="4" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>201</v>
       </c>
@@ -2203,8 +2299,8 @@
       <c r="E4" s="5">
         <v>2</v>
       </c>
-      <c r="F4" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F4" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>E2</v>
       </c>
       <c r="G4" s="5">
@@ -2240,7 +2336,7 @@
         <v>3</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>7.9861111111111049E-2</v>
       </c>
       <c r="R4" s="6" t="s">
@@ -2269,7 +2365,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.445601851851852E-2</v>
       </c>
       <c r="AD4" s="20">
@@ -2383,10 +2479,10 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY4" s="40">
+      <c r="BY4" s="31">
         <v>1</v>
       </c>
-      <c r="BZ4" s="55">
+      <c r="BZ4" s="54">
         <v>1.1342592592592592E-2</v>
       </c>
       <c r="CA4" s="33">
@@ -2453,9 +2549,31 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF4" s="35"/>
+      <c r="DF4" s="31"/>
+      <c r="DG4" s="34"/>
+      <c r="DH4" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI4" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ4" s="34">
+        <v>6.4004629629629628E-3</v>
+      </c>
+      <c r="DK4" s="33">
+        <f t="shared" si="26"/>
+        <v>1.4004629629629627E-3</v>
+      </c>
+      <c r="DL4" s="31"/>
+      <c r="DM4" s="34"/>
+      <c r="DN4" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO4" s="35"/>
     </row>
-    <row r="5" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>201</v>
       </c>
@@ -2471,8 +2589,8 @@
       <c r="E5" s="5">
         <v>3</v>
       </c>
-      <c r="F5" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F5" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>D3</v>
       </c>
       <c r="G5" s="5">
@@ -2508,7 +2626,7 @@
         <v>4</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.1388888888888928E-2</v>
       </c>
       <c r="R5" s="6" t="s">
@@ -2539,7 +2657,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>6.0231481481481476E-2</v>
       </c>
       <c r="AD5" s="20">
@@ -2560,10 +2678,10 @@
       </c>
       <c r="AI5" s="22"/>
       <c r="AJ5" s="29">
+        <v>6</v>
+      </c>
+      <c r="AK5" s="30">
         <v>4</v>
-      </c>
-      <c r="AK5" s="30">
-        <v>2</v>
       </c>
       <c r="AL5" s="31"/>
       <c r="AM5" s="34"/>
@@ -2571,11 +2689,15 @@
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="AO5" s="31"/>
-      <c r="AP5" s="32"/>
-      <c r="AQ5" s="33" t="str">
+      <c r="AO5" s="31">
+        <v>2</v>
+      </c>
+      <c r="AP5" s="34">
+        <v>3.7106481481481483E-2</v>
+      </c>
+      <c r="AQ5" s="33">
         <f t="shared" si="2"/>
-        <v>NA</v>
+        <v>3.3217592592592597E-2</v>
       </c>
       <c r="AR5" s="31"/>
       <c r="AS5" s="32"/>
@@ -2639,11 +2761,11 @@
         <v>1</v>
       </c>
       <c r="BT5" s="34">
-        <v>1.5891203703703703E-2</v>
+        <v>1.4965277777777777E-2</v>
       </c>
       <c r="BU5" s="33">
         <f t="shared" si="12"/>
-        <v>1.2002314814814815E-2</v>
+        <v>1.1076388888888889E-2</v>
       </c>
       <c r="BV5" s="31"/>
       <c r="BW5" s="32"/>
@@ -2651,8 +2773,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY5" s="40"/>
-      <c r="BZ5" s="55"/>
+      <c r="BY5" s="31"/>
+      <c r="BZ5" s="54"/>
       <c r="CA5" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -2663,11 +2785,15 @@
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
-      <c r="CE5" s="31"/>
-      <c r="CF5" s="32"/>
-      <c r="CG5" s="33" t="str">
+      <c r="CE5" s="31">
+        <v>1</v>
+      </c>
+      <c r="CF5" s="34">
+        <v>1.6724537037037038E-2</v>
+      </c>
+      <c r="CG5" s="33">
         <f t="shared" si="16"/>
-        <v>NA</v>
+        <v>1.283564814814815E-2</v>
       </c>
       <c r="CH5" s="31"/>
       <c r="CI5" s="32"/>
@@ -2717,9 +2843,35 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF5" s="35"/>
+      <c r="DF5" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG5" s="34">
+        <v>6.828703703703704E-3</v>
+      </c>
+      <c r="DH5" s="33">
+        <f t="shared" si="25"/>
+        <v>2.9398148148148157E-3</v>
+      </c>
+      <c r="DI5" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ5" s="34">
+        <v>1.5335648148148149E-2</v>
+      </c>
+      <c r="DK5" s="33">
+        <f t="shared" si="26"/>
+        <v>1.1446759259259261E-2</v>
+      </c>
+      <c r="DL5" s="31"/>
+      <c r="DM5" s="32"/>
+      <c r="DN5" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO5" s="35"/>
     </row>
-    <row r="6" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>201</v>
       </c>
@@ -2735,8 +2887,8 @@
       <c r="E6" s="5">
         <v>3</v>
       </c>
-      <c r="F6" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F6" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>E3</v>
       </c>
       <c r="G6" s="5">
@@ -2772,7 +2924,7 @@
         <v>3</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>0.10833333333333328</v>
       </c>
       <c r="R6" s="6" t="s">
@@ -2801,7 +2953,7 @@
       <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>5.0011574074074076E-2</v>
       </c>
       <c r="AD6" s="20">
@@ -2820,10 +2972,10 @@
       </c>
       <c r="AI6" s="22"/>
       <c r="AJ6" s="29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK6" s="30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL6" s="31">
         <v>1</v>
@@ -2881,11 +3033,11 @@
         <v>4</v>
       </c>
       <c r="BK6" s="34">
-        <v>7.2916666666666659E-3</v>
+        <v>5.3356481481481484E-3</v>
       </c>
       <c r="BL6" s="33">
         <f t="shared" si="9"/>
-        <v>2.6967592592592581E-3</v>
+        <v>7.407407407407406E-4</v>
       </c>
       <c r="BM6" s="31"/>
       <c r="BN6" s="32"/>
@@ -2919,10 +3071,10 @@
         <f t="shared" si="13"/>
         <v>2.6875000000000003E-2</v>
       </c>
-      <c r="BY6" s="40">
+      <c r="BY6" s="31">
         <v>2</v>
       </c>
-      <c r="BZ6" s="55">
+      <c r="BZ6" s="54">
         <v>3.0254629629629631E-2</v>
       </c>
       <c r="CA6" s="33">
@@ -2988,18 +3140,40 @@
         <v>NA</v>
       </c>
       <c r="DC6" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DD6" s="34">
-        <v>1.3344907407407408E-2</v>
+        <v>1.0231481481481482E-2</v>
       </c>
       <c r="DE6" s="33">
         <f t="shared" si="24"/>
-        <v>8.7500000000000008E-3</v>
-      </c>
-      <c r="DF6" s="35"/>
+        <v>5.6365740740740742E-3</v>
+      </c>
+      <c r="DF6" s="31"/>
+      <c r="DG6" s="32"/>
+      <c r="DH6" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ6" s="34">
+        <v>4.7453703703703703E-3</v>
+      </c>
+      <c r="DK6" s="33">
+        <f t="shared" si="26"/>
+        <v>1.5046296296296249E-4</v>
+      </c>
+      <c r="DL6" s="31"/>
+      <c r="DM6" s="34"/>
+      <c r="DN6" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO6" s="35"/>
     </row>
-    <row r="7" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>201</v>
       </c>
@@ -3015,8 +3189,8 @@
       <c r="E7" s="5">
         <v>1</v>
       </c>
-      <c r="F7" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F7" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>L1</v>
       </c>
       <c r="G7" s="5">
@@ -3052,7 +3226,7 @@
         <v>3</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>8.333333333333337E-2</v>
       </c>
       <c r="R7" s="6" t="s">
@@ -3081,7 +3255,7 @@
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>5.6006944444444449E-2</v>
       </c>
       <c r="AD7" s="20">
@@ -3155,15 +3329,11 @@
         <f t="shared" si="8"/>
         <v>NA</v>
       </c>
-      <c r="BJ7" s="31">
-        <v>1</v>
-      </c>
-      <c r="BK7" s="34">
-        <v>9.2129629629629627E-3</v>
-      </c>
-      <c r="BL7" s="33">
+      <c r="BJ7" s="31"/>
+      <c r="BK7" s="34"/>
+      <c r="BL7" s="33" t="str">
         <f t="shared" si="9"/>
-        <v>4.8263888888888887E-3</v>
+        <v>NA</v>
       </c>
       <c r="BM7" s="31"/>
       <c r="BN7" s="32"/>
@@ -3177,11 +3347,15 @@
         <f t="shared" si="11"/>
         <v>NA</v>
       </c>
-      <c r="BS7" s="31"/>
-      <c r="BT7" s="32"/>
-      <c r="BU7" s="33" t="str">
+      <c r="BS7" s="31">
+        <v>1</v>
+      </c>
+      <c r="BT7" s="34">
+        <v>9.1550925925925931E-3</v>
+      </c>
+      <c r="BU7" s="33">
         <f t="shared" si="12"/>
-        <v>NA</v>
+        <v>4.7685185185185192E-3</v>
       </c>
       <c r="BV7" s="31"/>
       <c r="BW7" s="32"/>
@@ -3189,8 +3363,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY7" s="40"/>
-      <c r="BZ7" s="55"/>
+      <c r="BY7" s="31"/>
+      <c r="BZ7" s="54"/>
       <c r="CA7" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -3271,9 +3445,27 @@
         <f t="shared" si="24"/>
         <v>2.1990740740740738E-4</v>
       </c>
-      <c r="DF7" s="35"/>
+      <c r="DF7" s="31"/>
+      <c r="DG7" s="32"/>
+      <c r="DH7" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI7" s="31"/>
+      <c r="DJ7" s="34"/>
+      <c r="DK7" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL7" s="31"/>
+      <c r="DM7" s="34"/>
+      <c r="DN7" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO7" s="35"/>
     </row>
-    <row r="8" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>201</v>
       </c>
@@ -3289,8 +3481,8 @@
       <c r="E8" s="5">
         <v>2</v>
       </c>
-      <c r="F8" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F8" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>L2</v>
       </c>
       <c r="G8" s="5">
@@ -3326,7 +3518,7 @@
         <v>3</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>7.4305555555555514E-2</v>
       </c>
       <c r="R8" s="6" t="s">
@@ -3355,7 +3547,7 @@
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>7.6365740740740748E-2</v>
       </c>
       <c r="AD8" s="20">
@@ -3394,7 +3586,7 @@
       <c r="AO8" s="31">
         <v>3</v>
       </c>
-      <c r="AP8" s="69">
+      <c r="AP8" s="68">
         <v>8.2407407407407412E-3</v>
       </c>
       <c r="AQ8" s="33">
@@ -3479,10 +3671,10 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY8" s="40">
+      <c r="BY8" s="31">
         <v>1</v>
       </c>
-      <c r="BZ8" s="55">
+      <c r="BZ8" s="54">
         <v>1.4444444444444446E-2</v>
       </c>
       <c r="CA8" s="33">
@@ -3526,19 +3718,19 @@
         <v>NA</v>
       </c>
       <c r="CT8" s="31"/>
-      <c r="CU8" s="69"/>
+      <c r="CU8" s="68"/>
       <c r="CV8" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW8" s="31"/>
-      <c r="CX8" s="69"/>
+      <c r="CX8" s="68"/>
       <c r="CY8" s="33" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
       <c r="CZ8" s="31"/>
-      <c r="DA8" s="69"/>
+      <c r="DA8" s="68"/>
       <c r="DB8" s="33" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
@@ -3546,16 +3738,38 @@
       <c r="DC8" s="31">
         <v>2</v>
       </c>
-      <c r="DD8" s="69">
+      <c r="DD8" s="68">
         <v>5.9837962962962961E-3</v>
       </c>
       <c r="DE8" s="33">
         <f t="shared" si="24"/>
         <v>1.4120370370370372E-3</v>
       </c>
-      <c r="DF8" s="35"/>
+      <c r="DF8" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG8" s="68">
+        <v>1.5393518518518518E-2</v>
+      </c>
+      <c r="DH8" s="33">
+        <f t="shared" si="25"/>
+        <v>1.082175925925926E-2</v>
+      </c>
+      <c r="DI8" s="31"/>
+      <c r="DJ8" s="68"/>
+      <c r="DK8" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL8" s="31"/>
+      <c r="DM8" s="68"/>
+      <c r="DN8" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO8" s="35"/>
     </row>
-    <row r="9" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>201</v>
       </c>
@@ -3571,8 +3785,8 @@
       <c r="E9" s="5">
         <v>1</v>
       </c>
-      <c r="F9" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F9" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>D1</v>
       </c>
       <c r="G9" s="5">
@@ -3608,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.9722222222222232E-2</v>
       </c>
       <c r="R9" s="6" t="s">
@@ -3637,7 +3851,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.6307870370370374E-2</v>
       </c>
       <c r="AD9" s="20">
@@ -3656,7 +3870,7 @@
       </c>
       <c r="AI9" s="22"/>
       <c r="AJ9" s="29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK9" s="30">
         <v>4</v>
@@ -3668,7 +3882,7 @@
         <v>NA</v>
       </c>
       <c r="AO9" s="31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AP9" s="34">
         <v>1.5196759259259259E-2</v>
@@ -3714,7 +3928,7 @@
         <v>NA</v>
       </c>
       <c r="BJ9" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK9" s="34">
         <v>4.0277777777777777E-3</v>
@@ -3747,8 +3961,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY9" s="40"/>
-      <c r="BZ9" s="55"/>
+      <c r="BY9" s="31"/>
+      <c r="BZ9" s="54"/>
       <c r="CA9" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -3794,32 +4008,62 @@
         <v>NA</v>
       </c>
       <c r="CT9" s="31"/>
-      <c r="CU9" s="55"/>
+      <c r="CU9" s="54"/>
       <c r="CV9" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW9" s="31"/>
-      <c r="CX9" s="55"/>
+      <c r="CX9" s="54"/>
       <c r="CY9" s="33" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
       <c r="CZ9" s="31"/>
-      <c r="DA9" s="55"/>
+      <c r="DA9" s="54"/>
       <c r="DB9" s="33" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
-      <c r="DC9" s="31"/>
-      <c r="DD9" s="55"/>
-      <c r="DE9" s="33" t="str">
+      <c r="DC9" s="31">
+        <v>1</v>
+      </c>
+      <c r="DD9" s="54">
+        <v>4.0277777777777777E-3</v>
+      </c>
+      <c r="DE9" s="33">
         <f t="shared" si="24"/>
-        <v>NA</v>
-      </c>
-      <c r="DF9" s="35"/>
+        <v>0</v>
+      </c>
+      <c r="DF9" s="31">
+        <v>5</v>
+      </c>
+      <c r="DG9" s="54">
+        <v>4.9189814814814816E-3</v>
+      </c>
+      <c r="DH9" s="33">
+        <f t="shared" si="25"/>
+        <v>8.9120370370370395E-4</v>
+      </c>
+      <c r="DI9" s="31"/>
+      <c r="DJ9" s="54"/>
+      <c r="DK9" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL9" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM9" s="54">
+        <v>3.5231481481481482E-2</v>
+      </c>
+      <c r="DN9" s="33">
+        <f t="shared" si="27"/>
+        <v>3.1203703703703706E-2</v>
+      </c>
+      <c r="DO9" s="35"/>
     </row>
-    <row r="10" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>201</v>
       </c>
@@ -3835,8 +4079,8 @@
       <c r="E10" s="5">
         <v>3</v>
       </c>
-      <c r="F10" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F10" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>L3</v>
       </c>
       <c r="G10" s="5">
@@ -3872,7 +4116,7 @@
         <v>2</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.4861111111111027E-2</v>
       </c>
       <c r="R10" s="6" t="s">
@@ -3899,7 +4143,7 @@
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.7581018518518522E-2</v>
       </c>
       <c r="AD10" s="20">
@@ -4013,8 +4257,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY10" s="40"/>
-      <c r="BZ10" s="55"/>
+      <c r="BY10" s="31"/>
+      <c r="BZ10" s="54"/>
       <c r="CA10" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -4087,9 +4331,27 @@
         <f t="shared" si="24"/>
         <v>3.0092592592592497E-4</v>
       </c>
-      <c r="DF10" s="35"/>
+      <c r="DF10" s="31"/>
+      <c r="DG10" s="34"/>
+      <c r="DH10" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI10" s="31"/>
+      <c r="DJ10" s="34"/>
+      <c r="DK10" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL10" s="31"/>
+      <c r="DM10" s="34"/>
+      <c r="DN10" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO10" s="35"/>
     </row>
-    <row r="11" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>201</v>
       </c>
@@ -4105,8 +4367,8 @@
       <c r="E11" s="5">
         <v>6</v>
       </c>
-      <c r="F11" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F11" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>L6</v>
       </c>
       <c r="G11" s="5">
@@ -4142,7 +4404,7 @@
         <v>3</v>
       </c>
       <c r="Q11" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>8.6111111111111138E-2</v>
       </c>
       <c r="R11" s="6" t="s">
@@ -4171,7 +4433,7 @@
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>7.6435185185185189E-2</v>
       </c>
       <c r="AD11" s="20">
@@ -4283,8 +4545,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY11" s="40"/>
-      <c r="BZ11" s="55"/>
+      <c r="BY11" s="31"/>
+      <c r="BZ11" s="54"/>
       <c r="CA11" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -4349,9 +4611,27 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF11" s="35"/>
+      <c r="DF11" s="31"/>
+      <c r="DG11" s="34"/>
+      <c r="DH11" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI11" s="31"/>
+      <c r="DJ11" s="34"/>
+      <c r="DK11" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL11" s="31"/>
+      <c r="DM11" s="34"/>
+      <c r="DN11" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO11" s="35"/>
     </row>
-    <row r="12" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>201</v>
       </c>
@@ -4367,8 +4647,8 @@
       <c r="E12" s="5">
         <v>4</v>
       </c>
-      <c r="F12" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F12" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>D4</v>
       </c>
       <c r="G12" s="5">
@@ -4404,7 +4684,7 @@
         <v>3</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>8.333333333333337E-2</v>
       </c>
       <c r="R12" s="6" t="s">
@@ -4433,7 +4713,7 @@
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>5.0578703703703709E-2</v>
       </c>
       <c r="AD12" s="20">
@@ -4541,75 +4821,101 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY12" s="40"/>
-      <c r="BZ12" s="55"/>
+      <c r="BY12" s="31"/>
+      <c r="BZ12" s="54"/>
       <c r="CA12" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
       </c>
       <c r="CB12" s="31"/>
-      <c r="CC12" s="69"/>
+      <c r="CC12" s="68"/>
       <c r="CD12" s="33" t="str">
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE12" s="31"/>
-      <c r="CF12" s="69"/>
+      <c r="CF12" s="68"/>
       <c r="CG12" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CH12" s="31"/>
-      <c r="CI12" s="69"/>
+      <c r="CI12" s="68"/>
       <c r="CJ12" s="33" t="str">
         <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CK12" s="31"/>
-      <c r="CL12" s="69"/>
+      <c r="CL12" s="68"/>
       <c r="CM12" s="33" t="str">
         <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CN12" s="31"/>
-      <c r="CO12" s="69"/>
+      <c r="CO12" s="68"/>
       <c r="CP12" s="33" t="str">
         <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CQ12" s="31"/>
-      <c r="CR12" s="69"/>
+      <c r="CR12" s="68"/>
       <c r="CS12" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT12" s="31"/>
-      <c r="CU12" s="69"/>
+      <c r="CU12" s="68"/>
       <c r="CV12" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
       <c r="CW12" s="31"/>
-      <c r="CX12" s="69"/>
+      <c r="CX12" s="68"/>
       <c r="CY12" s="33" t="str">
         <f t="shared" si="22"/>
         <v>NA</v>
       </c>
       <c r="CZ12" s="31"/>
-      <c r="DA12" s="69"/>
+      <c r="DA12" s="68"/>
       <c r="DB12" s="33" t="str">
         <f t="shared" si="23"/>
         <v>NA</v>
       </c>
       <c r="DC12" s="31"/>
-      <c r="DD12" s="69"/>
+      <c r="DD12" s="68"/>
       <c r="DE12" s="33" t="str">
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF12" s="35"/>
+      <c r="DF12" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG12" s="68">
+        <v>2.7546296296296298E-2</v>
+      </c>
+      <c r="DH12" s="33">
+        <f t="shared" si="25"/>
+        <v>2.3819444444444445E-2</v>
+      </c>
+      <c r="DI12" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ12" s="68">
+        <v>3.7048611111111109E-2</v>
+      </c>
+      <c r="DK12" s="33">
+        <f t="shared" si="26"/>
+        <v>3.3321759259259259E-2</v>
+      </c>
+      <c r="DL12" s="31"/>
+      <c r="DM12" s="68"/>
+      <c r="DN12" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO12" s="35"/>
     </row>
-    <row r="13" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>201</v>
       </c>
@@ -4625,8 +4931,8 @@
       <c r="E13" s="5">
         <v>5</v>
       </c>
-      <c r="F13" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F13" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>D5</v>
       </c>
       <c r="G13" s="5">
@@ -4662,7 +4968,7 @@
         <v>3</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>7.3611111111111072E-2</v>
       </c>
       <c r="R13" s="6" t="s">
@@ -4691,7 +4997,7 @@
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>5.4942129629629625E-2</v>
       </c>
       <c r="AD13" s="20">
@@ -4712,7 +5018,7 @@
       </c>
       <c r="AI13" s="22"/>
       <c r="AJ13" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK13" s="30">
         <v>0</v>
@@ -4795,8 +5101,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY13" s="40"/>
-      <c r="BZ13" s="55"/>
+      <c r="BY13" s="31"/>
+      <c r="BZ13" s="54"/>
       <c r="CA13" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -4861,9 +5167,31 @@
         <f t="shared" si="24"/>
         <v>NA</v>
       </c>
-      <c r="DF13" s="35"/>
+      <c r="DF13" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG13" s="34">
+        <v>2.8518518518518519E-2</v>
+      </c>
+      <c r="DH13" s="33">
+        <f t="shared" si="25"/>
+        <v>2.3692129629629632E-2</v>
+      </c>
+      <c r="DI13" s="31"/>
+      <c r="DJ13" s="32"/>
+      <c r="DK13" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL13" s="31"/>
+      <c r="DM13" s="32"/>
+      <c r="DN13" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DO13" s="35"/>
     </row>
-    <row r="14" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>201</v>
       </c>
@@ -4879,8 +5207,8 @@
       <c r="E14" s="5">
         <v>5</v>
       </c>
-      <c r="F14" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F14" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>L5</v>
       </c>
       <c r="G14" s="5">
@@ -4916,7 +5244,7 @@
         <v>3</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>7.2222222222222077E-2</v>
       </c>
       <c r="R14" s="6" t="s">
@@ -4945,7 +5273,7 @@
       <c r="AA14" s="20"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>5.6261574074074075E-2</v>
       </c>
       <c r="AD14" s="20">
@@ -4955,7 +5283,7 @@
         <v>8.9351851851851866E-3</v>
       </c>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF19" si="28">AC14-AD14-AE14</f>
+        <f t="shared" ref="AF14:AF19" si="31">AC14-AD14-AE14</f>
         <v>4.297453703703704E-2</v>
       </c>
       <c r="AG14" s="21">
@@ -4974,13 +5302,13 @@
       <c r="AL14" s="31"/>
       <c r="AM14" s="32"/>
       <c r="AN14" s="33" t="str">
-        <f t="shared" ref="AN14:AN19" si="29">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN19" si="32">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AO14" s="31"/>
       <c r="AP14" s="32"/>
       <c r="AQ14" s="33" t="str">
-        <f t="shared" ref="AQ14:AQ19" si="30">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ19" si="33">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AR14" s="31">
@@ -4990,13 +5318,13 @@
         <v>1.1643518518518518E-2</v>
       </c>
       <c r="AT14" s="33">
-        <f t="shared" ref="AT14:AT19" si="31">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT19" si="34">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>7.2916666666666668E-3</v>
       </c>
       <c r="AU14" s="31"/>
       <c r="AV14" s="32"/>
       <c r="AW14" s="33" t="str">
-        <f t="shared" ref="AW14:AW19" si="32">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW19" si="35">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="31"/>
@@ -5008,43 +5336,43 @@
       <c r="BA14" s="31"/>
       <c r="BB14" s="34"/>
       <c r="BC14" s="33" t="str">
-        <f t="shared" ref="BC14:BC19" si="33">IF(BA14=0,"NA",BB14-$AD14)</f>
+        <f t="shared" ref="BC14:BC19" si="36">IF(BA14=0,"NA",BB14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BD14" s="31"/>
       <c r="BE14" s="32"/>
       <c r="BF14" s="33" t="str">
-        <f t="shared" ref="BF14:BF19" si="34">IF(BD14=0,"NA",BE14-$AD14)</f>
+        <f t="shared" ref="BF14:BF19" si="37">IF(BD14=0,"NA",BE14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BG14" s="31"/>
       <c r="BH14" s="34"/>
       <c r="BI14" s="33" t="str">
-        <f t="shared" ref="BI14:BI19" si="35">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI19" si="38">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="31"/>
       <c r="BK14" s="34"/>
       <c r="BL14" s="33" t="str">
-        <f t="shared" ref="BL14:BL19" si="36">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <f t="shared" ref="BL14:BL19" si="39">IF(BJ14=0,"NA",BK14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BM14" s="31"/>
       <c r="BN14" s="32"/>
       <c r="BO14" s="33" t="str">
-        <f t="shared" ref="BO14:BO19" si="37">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <f t="shared" ref="BO14:BO19" si="40">IF(BM14=0,"NA",BN14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BP14" s="31"/>
       <c r="BQ14" s="32"/>
       <c r="BR14" s="33" t="str">
-        <f t="shared" ref="BR14:BR19" si="38">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR19" si="41">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="31"/>
       <c r="BT14" s="34"/>
       <c r="BU14" s="33" t="str">
-        <f t="shared" ref="BU14:BU19" si="39">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <f t="shared" ref="BU14:BU19" si="42">IF(BS14=0,"NA",BT14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BV14" s="31"/>
@@ -5053,8 +5381,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY14" s="40"/>
-      <c r="BZ14" s="55"/>
+      <c r="BY14" s="31"/>
+      <c r="BZ14" s="54"/>
       <c r="CA14" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -5120,12 +5448,38 @@
         <v>4.4212962962962956E-3</v>
       </c>
       <c r="DE14" s="33">
-        <f t="shared" ref="DE14:DE19" si="40">IF(DC14=0,"NA",DD14-$AD14)</f>
+        <f t="shared" si="24"/>
         <v>6.9444444444444024E-5</v>
       </c>
-      <c r="DF14" s="35"/>
+      <c r="DF14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG14" s="34">
+        <v>9.8263888888888897E-3</v>
+      </c>
+      <c r="DH14" s="33">
+        <f t="shared" si="25"/>
+        <v>5.4745370370370382E-3</v>
+      </c>
+      <c r="DI14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ14" s="34">
+        <v>2.6354166666666668E-2</v>
+      </c>
+      <c r="DK14" s="33">
+        <f t="shared" si="26"/>
+        <v>2.2002314814814815E-2</v>
+      </c>
+      <c r="DL14" s="31"/>
+      <c r="DM14" s="34"/>
+      <c r="DN14" s="33" t="str">
+        <f t="shared" ref="DN14:DN19" si="43">IF(DL14=0,"NA",DM14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="DO14" s="35"/>
     </row>
-    <row r="15" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>201</v>
       </c>
@@ -5141,8 +5495,8 @@
       <c r="E15" s="5">
         <v>4</v>
       </c>
-      <c r="F15" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F15" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>L4</v>
       </c>
       <c r="G15" s="5">
@@ -5178,7 +5532,7 @@
         <v>3</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.8333333333333459E-2</v>
       </c>
       <c r="R15" s="6" t="s">
@@ -5207,7 +5561,7 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>5.8854166666666673E-2</v>
       </c>
       <c r="AD15" s="20">
@@ -5217,7 +5571,7 @@
         <v>1.2719907407407407E-2</v>
       </c>
       <c r="AF15" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4.2094907407407414E-2</v>
       </c>
       <c r="AG15" s="21">
@@ -5236,7 +5590,7 @@
       <c r="AL15" s="31"/>
       <c r="AM15" s="34"/>
       <c r="AN15" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO15" s="31">
@@ -5246,7 +5600,7 @@
         <v>1.9988425925925927E-2</v>
       </c>
       <c r="AQ15" s="33">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>1.5949074074074074E-2</v>
       </c>
       <c r="AR15" s="31">
@@ -5256,13 +5610,13 @@
         <v>4.0381944444444443E-2</v>
       </c>
       <c r="AT15" s="33">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>3.6342592592592593E-2</v>
       </c>
       <c r="AU15" s="31"/>
       <c r="AV15" s="32"/>
       <c r="AW15" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="31"/>
@@ -5274,19 +5628,19 @@
       <c r="BA15" s="31"/>
       <c r="BB15" s="32"/>
       <c r="BC15" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG15" s="31"/>
       <c r="BH15" s="34"/>
       <c r="BI15" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="31">
@@ -5296,53 +5650,53 @@
         <v>4.3749999999999995E-3</v>
       </c>
       <c r="BL15" s="33">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>3.3564814814814742E-4</v>
       </c>
       <c r="BM15" s="31"/>
       <c r="BN15" s="32"/>
       <c r="BO15" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP15" s="31"/>
       <c r="BQ15" s="32"/>
       <c r="BR15" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS15" s="31"/>
       <c r="BT15" s="34"/>
       <c r="BU15" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV15" s="31"/>
-      <c r="BW15" s="69"/>
+      <c r="BW15" s="68"/>
       <c r="BX15" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY15" s="40"/>
-      <c r="BZ15" s="55"/>
+      <c r="BY15" s="31"/>
+      <c r="BZ15" s="54"/>
       <c r="CA15" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
       </c>
       <c r="CB15" s="31"/>
-      <c r="CC15" s="69"/>
+      <c r="CC15" s="68"/>
       <c r="CD15" s="33" t="str">
         <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE15" s="31"/>
-      <c r="CF15" s="69"/>
+      <c r="CF15" s="68"/>
       <c r="CG15" s="33" t="str">
         <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CH15" s="31"/>
-      <c r="CI15" s="69"/>
+      <c r="CI15" s="68"/>
       <c r="CJ15" s="33" t="str">
         <f t="shared" si="17"/>
         <v>NA</v>
@@ -5390,12 +5744,34 @@
         <v>4.8726851851851856E-3</v>
       </c>
       <c r="DE15" s="33">
-        <f t="shared" si="40"/>
+        <f t="shared" si="24"/>
         <v>8.333333333333335E-4</v>
       </c>
-      <c r="DF15" s="35"/>
+      <c r="DF15" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG15" s="34">
+        <v>1.1342592592592593E-2</v>
+      </c>
+      <c r="DH15" s="33">
+        <f t="shared" si="25"/>
+        <v>7.3032407407407412E-3</v>
+      </c>
+      <c r="DI15" s="31"/>
+      <c r="DJ15" s="32"/>
+      <c r="DK15" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DL15" s="31"/>
+      <c r="DM15" s="34"/>
+      <c r="DN15" s="33" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DO15" s="35"/>
     </row>
-    <row r="16" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>201</v>
       </c>
@@ -5411,8 +5787,8 @@
       <c r="E16" s="5">
         <v>6</v>
       </c>
-      <c r="F16" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F16" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>D6</v>
       </c>
       <c r="G16" s="5">
@@ -5448,7 +5824,7 @@
         <v>4</v>
       </c>
       <c r="Q16" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.6250000000000022E-2</v>
       </c>
       <c r="R16" s="6" t="s">
@@ -5479,7 +5855,7 @@
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
       <c r="AC16" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>6.9143518518518521E-2</v>
       </c>
       <c r="AD16" s="20">
@@ -5489,7 +5865,7 @@
         <v>2.0254629629629629E-2</v>
       </c>
       <c r="AF16" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4.5081018518518527E-2</v>
       </c>
       <c r="AG16" s="21">
@@ -5508,25 +5884,25 @@
       <c r="AL16" s="31"/>
       <c r="AM16" s="34"/>
       <c r="AN16" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO16" s="31"/>
       <c r="AP16" s="34"/>
       <c r="AQ16" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AR16" s="31"/>
       <c r="AS16" s="34"/>
       <c r="AT16" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AU16" s="31"/>
       <c r="AV16" s="34"/>
       <c r="AW16" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="31"/>
@@ -5538,43 +5914,43 @@
       <c r="BA16" s="31"/>
       <c r="BB16" s="34"/>
       <c r="BC16" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="BD16" s="31"/>
       <c r="BE16" s="34"/>
       <c r="BF16" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG16" s="31"/>
       <c r="BH16" s="34"/>
-      <c r="BI16" s="55" t="str">
-        <f t="shared" si="35"/>
-        <v>NA</v>
-      </c>
-      <c r="BJ16" s="40"/>
+      <c r="BI16" s="54" t="str">
+        <f t="shared" si="38"/>
+        <v>NA</v>
+      </c>
+      <c r="BJ16" s="31"/>
       <c r="BK16" s="34"/>
       <c r="BL16" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BM16" s="31"/>
       <c r="BN16" s="32"/>
       <c r="BO16" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP16" s="31"/>
       <c r="BQ16" s="32"/>
       <c r="BR16" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="31"/>
-      <c r="BT16" s="55"/>
+      <c r="BT16" s="54"/>
       <c r="BU16" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV16" s="31"/>
@@ -5583,8 +5959,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY16" s="40"/>
-      <c r="BZ16" s="55"/>
+      <c r="BY16" s="31"/>
+      <c r="BZ16" s="54"/>
       <c r="CA16" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -5646,16 +6022,42 @@
       <c r="DC16" s="31"/>
       <c r="DD16" s="34"/>
       <c r="DE16" s="33" t="str">
-        <f t="shared" si="40"/>
-        <v>NA</v>
-      </c>
-      <c r="DF16" s="35"/>
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF16" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG16" s="34">
+        <v>4.1504629629629627E-2</v>
+      </c>
+      <c r="DH16" s="33">
+        <f t="shared" si="25"/>
+        <v>3.7696759259259256E-2</v>
+      </c>
+      <c r="DI16" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ16" s="34">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="DK16" s="33">
+        <f t="shared" si="26"/>
+        <v>0.43091435185185184</v>
+      </c>
+      <c r="DL16" s="31"/>
+      <c r="DM16" s="34"/>
+      <c r="DN16" s="33" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DO16" s="35"/>
     </row>
-    <row r="17" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B17" s="89">
+      <c r="B17" s="83">
         <v>45297</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -5667,8 +6069,8 @@
       <c r="E17" s="5">
         <v>6</v>
       </c>
-      <c r="F17" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F17" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>E6</v>
       </c>
       <c r="G17" s="5">
@@ -5704,7 +6106,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>7.3611111111111127E-2</v>
       </c>
       <c r="R17" s="6" t="s">
@@ -5733,7 +6135,7 @@
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.4189814814814821E-2</v>
       </c>
       <c r="AD17" s="20">
@@ -5741,7 +6143,7 @@
       </c>
       <c r="AE17" s="20"/>
       <c r="AF17" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4.0358796296296302E-2</v>
       </c>
       <c r="AG17" s="21">
@@ -5760,25 +6162,25 @@
       <c r="AL17" s="31"/>
       <c r="AM17" s="34"/>
       <c r="AN17" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO17" s="31"/>
       <c r="AP17" s="34"/>
       <c r="AQ17" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AR17" s="31"/>
       <c r="AS17" s="34"/>
       <c r="AT17" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AU17" s="31"/>
       <c r="AV17" s="34"/>
       <c r="AW17" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="31"/>
@@ -5790,41 +6192,41 @@
       <c r="BA17" s="31"/>
       <c r="BB17" s="34"/>
       <c r="BC17" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="BD17" s="31"/>
       <c r="BE17" s="34"/>
       <c r="BF17" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG17" s="31"/>
       <c r="BH17" s="34"/>
       <c r="BI17" s="33" t="str">
-        <f t="shared" si="35"/>
-        <v>NA</v>
-      </c>
-      <c r="BJ17" s="40">
+        <f t="shared" si="38"/>
+        <v>NA</v>
+      </c>
+      <c r="BJ17" s="31">
         <v>3</v>
       </c>
       <c r="BK17" s="34">
         <v>3.8541666666666668E-3</v>
       </c>
       <c r="BL17" s="33">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>2.3148148148148442E-5</v>
       </c>
-      <c r="BM17" s="40"/>
+      <c r="BM17" s="31"/>
       <c r="BN17" s="34"/>
       <c r="BO17" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="BP17" s="40"/>
+        <f t="shared" si="40"/>
+        <v>NA</v>
+      </c>
+      <c r="BP17" s="31"/>
       <c r="BQ17" s="34"/>
       <c r="BR17" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS17" s="31">
@@ -5834,7 +6236,7 @@
         <v>2.4965277777777781E-2</v>
       </c>
       <c r="BU17" s="33">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>2.1134259259259262E-2</v>
       </c>
       <c r="BV17" s="31"/>
@@ -5843,8 +6245,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY17" s="40"/>
-      <c r="BZ17" s="55"/>
+      <c r="BY17" s="31"/>
+      <c r="BZ17" s="54"/>
       <c r="CA17" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -5910,16 +6312,38 @@
       <c r="DC17" s="31"/>
       <c r="DD17" s="34"/>
       <c r="DE17" s="33" t="str">
-        <f t="shared" si="40"/>
-        <v>NA</v>
-      </c>
-      <c r="DF17" s="35"/>
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF17" s="31"/>
+      <c r="DG17" s="34"/>
+      <c r="DH17" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI17" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ17" s="34">
+        <v>1.1342592592592593E-2</v>
+      </c>
+      <c r="DK17" s="33">
+        <f t="shared" si="26"/>
+        <v>7.511574074074075E-3</v>
+      </c>
+      <c r="DL17" s="31"/>
+      <c r="DM17" s="34"/>
+      <c r="DN17" s="33" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DO17" s="35"/>
     </row>
-    <row r="18" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B18" s="89">
+      <c r="B18" s="83">
         <v>45297</v>
       </c>
       <c r="C18" s="9" t="s">
@@ -5931,8 +6355,8 @@
       <c r="E18" s="5">
         <v>4</v>
       </c>
-      <c r="F18" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F18" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>E4</v>
       </c>
       <c r="G18" s="5">
@@ -5968,7 +6392,7 @@
         <v>4</v>
       </c>
       <c r="Q18" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>7.0138888888888917E-2</v>
       </c>
       <c r="R18" s="6" t="s">
@@ -5999,7 +6423,7 @@
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>6.0335648148148145E-2</v>
       </c>
       <c r="AD18" s="20">
@@ -6009,7 +6433,7 @@
         <v>1.4201388888888888E-2</v>
       </c>
       <c r="AF18" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4.2314814814814812E-2</v>
       </c>
       <c r="AG18" s="21">
@@ -6028,25 +6452,25 @@
       <c r="AL18" s="31"/>
       <c r="AM18" s="34"/>
       <c r="AN18" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO18" s="31"/>
       <c r="AP18" s="34"/>
       <c r="AQ18" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AR18" s="31"/>
       <c r="AS18" s="34"/>
       <c r="AT18" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AU18" s="31"/>
       <c r="AV18" s="34"/>
       <c r="AW18" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX18" s="31"/>
@@ -6058,19 +6482,19 @@
       <c r="BA18" s="31"/>
       <c r="BB18" s="34"/>
       <c r="BC18" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="BD18" s="31"/>
       <c r="BE18" s="34"/>
       <c r="BF18" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG18" s="31"/>
       <c r="BH18" s="34"/>
       <c r="BI18" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="31">
@@ -6080,19 +6504,19 @@
         <v>1.7048611111111112E-2</v>
       </c>
       <c r="BL18" s="33">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>1.3229166666666667E-2</v>
       </c>
       <c r="BM18" s="31"/>
       <c r="BN18" s="34"/>
       <c r="BO18" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP18" s="31"/>
       <c r="BQ18" s="34"/>
       <c r="BR18" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="31">
@@ -6102,7 +6526,7 @@
         <v>2.3391203703703702E-2</v>
       </c>
       <c r="BU18" s="33">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>1.9571759259259257E-2</v>
       </c>
       <c r="BV18" s="31"/>
@@ -6111,8 +6535,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY18" s="40"/>
-      <c r="BZ18" s="55"/>
+      <c r="BY18" s="31"/>
+      <c r="BZ18" s="54"/>
       <c r="CA18" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -6174,16 +6598,38 @@
       <c r="DC18" s="31"/>
       <c r="DD18" s="34"/>
       <c r="DE18" s="33" t="str">
-        <f t="shared" si="40"/>
-        <v>NA</v>
-      </c>
-      <c r="DF18" s="35"/>
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF18" s="31"/>
+      <c r="DG18" s="34"/>
+      <c r="DH18" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI18" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ18" s="34">
+        <v>1.5729166666666666E-2</v>
+      </c>
+      <c r="DK18" s="33">
+        <f t="shared" si="26"/>
+        <v>1.1909722222222221E-2</v>
+      </c>
+      <c r="DL18" s="31"/>
+      <c r="DM18" s="34"/>
+      <c r="DN18" s="33" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="DO18" s="35"/>
     </row>
-    <row r="19" spans="1:110" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:119" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B19" s="89">
+      <c r="B19" s="83">
         <v>45297</v>
       </c>
       <c r="C19" s="9" t="s">
@@ -6195,8 +6641,8 @@
       <c r="E19" s="5">
         <v>5</v>
       </c>
-      <c r="F19" s="74" t="str">
-        <f t="shared" si="25"/>
+      <c r="F19" s="72" t="str">
+        <f t="shared" si="28"/>
         <v>E5</v>
       </c>
       <c r="G19" s="5">
@@ -6232,7 +6678,7 @@
         <v>4</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>5.2083333333333259E-2</v>
       </c>
       <c r="R19" s="6" t="s">
@@ -6263,7 +6709,7 @@
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>5.6354166666666664E-2</v>
       </c>
       <c r="AD19" s="20">
@@ -6273,7 +6719,7 @@
         <v>1.1076388888888887E-2</v>
       </c>
       <c r="AF19" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>4.1342592592592591E-2</v>
       </c>
       <c r="AG19" s="21">
@@ -6292,25 +6738,25 @@
       <c r="AL19" s="31"/>
       <c r="AM19" s="34"/>
       <c r="AN19" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="32"/>
         <v>NA</v>
       </c>
       <c r="AO19" s="31"/>
       <c r="AP19" s="34"/>
       <c r="AQ19" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AR19" s="31"/>
       <c r="AS19" s="34"/>
       <c r="AT19" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AU19" s="31"/>
       <c r="AV19" s="34"/>
       <c r="AW19" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AX19" s="31"/>
@@ -6322,19 +6768,19 @@
       <c r="BA19" s="31"/>
       <c r="BB19" s="34"/>
       <c r="BC19" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="BD19" s="31"/>
       <c r="BE19" s="34"/>
       <c r="BF19" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BG19" s="31"/>
       <c r="BH19" s="34"/>
       <c r="BI19" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="31">
@@ -6344,25 +6790,25 @@
         <v>4.2476851851851851E-3</v>
       </c>
       <c r="BL19" s="33">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>3.1249999999999941E-4</v>
       </c>
       <c r="BM19" s="31"/>
       <c r="BN19" s="34"/>
       <c r="BO19" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP19" s="31"/>
       <c r="BQ19" s="34"/>
       <c r="BR19" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="31"/>
       <c r="BT19" s="32"/>
       <c r="BU19" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV19" s="31"/>
@@ -6371,8 +6817,8 @@
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY19" s="40"/>
-      <c r="BZ19" s="55"/>
+      <c r="BY19" s="31"/>
+      <c r="BZ19" s="54"/>
       <c r="CA19" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
@@ -6434,10 +6880,36 @@
       <c r="DC19" s="31"/>
       <c r="DD19" s="34"/>
       <c r="DE19" s="33" t="str">
-        <f t="shared" si="40"/>
-        <v>NA</v>
-      </c>
-      <c r="DF19" s="35"/>
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DF19" s="31"/>
+      <c r="DG19" s="34"/>
+      <c r="DH19" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DI19" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ19" s="34">
+        <v>6.145833333333333E-3</v>
+      </c>
+      <c r="DK19" s="33">
+        <f t="shared" si="26"/>
+        <v>2.2106481481481473E-3</v>
+      </c>
+      <c r="DL19" s="31">
+        <v>1</v>
+      </c>
+      <c r="DM19" s="34">
+        <v>1.2118055555555556E-2</v>
+      </c>
+      <c r="DN19" s="33">
+        <f t="shared" si="43"/>
+        <v>8.1828703703703699E-3</v>
+      </c>
+      <c r="DO19" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6475,10 +6947,10 @@
       <c r="B2">
         <v>93</v>
       </c>
-      <c r="C2" s="90">
+      <c r="C2" s="84">
         <v>45444</v>
       </c>
-      <c r="D2" s="54">
+      <c r="D2" s="53">
         <v>0.32083333333333336</v>
       </c>
     </row>
@@ -6489,10 +6961,10 @@
       <c r="B3">
         <v>88</v>
       </c>
-      <c r="C3" s="90">
+      <c r="C3" s="84">
         <v>45442</v>
       </c>
-      <c r="D3" s="54">
+      <c r="D3" s="53">
         <v>0.68472222222222223</v>
       </c>
     </row>
@@ -6503,10 +6975,10 @@
       <c r="B4">
         <v>89</v>
       </c>
-      <c r="C4" s="90">
+      <c r="C4" s="84">
         <v>45442</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="53">
         <v>0.6791666666666667</v>
       </c>
     </row>
@@ -6517,37 +6989,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F89D226-4FD3-43E7-AD2C-117D056F41E4}">
-  <dimension ref="A1:CW22"/>
+  <dimension ref="A1:CU22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="22" max="28" width="8.7265625" style="1"/>
     <col min="36" max="36" width="14.90625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="8.7265625" style="84"/>
-    <col min="42" max="42" width="14.453125" style="84" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="8.7265625" style="84"/>
-    <col min="45" max="45" width="10.7265625" style="84" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="8.7265625" style="84"/>
-    <col min="48" max="48" width="10.6328125" style="84" bestFit="1" customWidth="1"/>
-    <col min="49" max="50" width="8.7265625" style="84"/>
-    <col min="51" max="51" width="10.6328125" style="84" bestFit="1" customWidth="1"/>
-    <col min="52" max="53" width="8.7265625" style="84"/>
-    <col min="54" max="54" width="12.81640625" style="84" bestFit="1" customWidth="1"/>
-    <col min="55" max="56" width="8.7265625" style="84"/>
-    <col min="57" max="57" width="8.90625" style="84" bestFit="1" customWidth="1"/>
-    <col min="58" max="75" width="8.7265625" style="84"/>
-    <col min="76" max="76" width="8.7265625" style="85"/>
-    <col min="77" max="77" width="8.7265625" style="84"/>
-    <col min="78" max="78" width="9.36328125" style="84" bestFit="1" customWidth="1"/>
-    <col min="79" max="83" width="8.7265625" style="84"/>
-    <col min="84" max="84" width="18.36328125" style="84" bestFit="1" customWidth="1"/>
-    <col min="85" max="95" width="8.7265625" style="84"/>
-    <col min="96" max="96" width="11.1796875" style="84" bestFit="1" customWidth="1"/>
-    <col min="97" max="98" width="8.7265625" style="84"/>
-    <col min="99" max="99" width="11.1796875" style="84" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="13.90625" style="84" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="8.7265625" style="84"/>
+    <col min="42" max="42" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:99" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6563,7 +7022,7 @@
       <c r="D1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="73" t="s">
+      <c r="E1" s="71" t="s">
         <v>98</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -6656,7 +7115,7 @@
       <c r="AI1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="AJ1" s="58" t="s">
+      <c r="AJ1" s="57" t="s">
         <v>11</v>
       </c>
       <c r="AK1" s="26" t="s">
@@ -6670,29 +7129,29 @@
       </c>
     </row>
     <row r="2" spans="1:99" ht="145" x14ac:dyDescent="0.35">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="74" t="s">
+      <c r="E2" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="43"/>
-      <c r="H2" s="45" t="s">
+      <c r="G2" s="42"/>
+      <c r="H2" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="I2" s="42" t="s">
         <v>74</v>
       </c>
       <c r="J2" s="7" t="s">
@@ -6701,124 +7160,124 @@
       <c r="K2" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="L2" s="43" t="s">
+      <c r="L2" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="M2" s="43" t="s">
+      <c r="M2" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="N2" s="43" t="s">
+      <c r="N2" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="O2" s="43" t="s">
+      <c r="O2" s="42" t="s">
         <v>75</v>
       </c>
       <c r="P2" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="Q2" s="45" t="s">
+      <c r="Q2" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="R2" s="43" t="s">
+      <c r="R2" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="S2" s="43" t="s">
+      <c r="S2" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="T2" s="43" t="s">
+      <c r="T2" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="U2" s="46"/>
-      <c r="V2" s="47" t="s">
+      <c r="U2" s="45"/>
+      <c r="V2" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="W2" s="48" t="s">
+      <c r="W2" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="X2" s="48" t="s">
+      <c r="X2" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="Y2" s="48" t="s">
+      <c r="Y2" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="Z2" s="48" t="s">
+      <c r="Z2" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="AA2" s="48" t="s">
+      <c r="AA2" s="47" t="s">
         <v>78</v>
       </c>
       <c r="AB2" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="AC2" s="48" t="s">
+      <c r="AC2" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="AD2" s="48" t="s">
+      <c r="AD2" s="47" t="s">
         <v>80</v>
       </c>
       <c r="AE2" s="20" t="e">
         <f t="shared" ref="AE2:AE22" si="0">AB2-AC2-AD2</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AF2" s="49" t="s">
+      <c r="AF2" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="AG2" s="49" t="s">
+      <c r="AG2" s="48" t="s">
         <v>81</v>
       </c>
       <c r="AH2" s="22"/>
-      <c r="AI2" s="50" t="s">
+      <c r="AI2" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="AJ2" s="51" t="s">
+      <c r="AJ2" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="AK2" s="52" t="s">
+      <c r="AK2" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="AL2" s="53" t="s">
+      <c r="AL2" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="AM2" s="55" t="s">
+      <c r="AM2" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="AO2" s="86"/>
-      <c r="AP2" s="86"/>
-      <c r="AS2" s="86"/>
-      <c r="AV2" s="86"/>
-      <c r="AY2" s="86"/>
-      <c r="BB2" s="86"/>
-      <c r="BE2" s="86"/>
-      <c r="BH2" s="86"/>
-      <c r="BK2" s="86"/>
-      <c r="BN2" s="86"/>
-      <c r="BQ2" s="86"/>
-      <c r="BS2" s="87"/>
-      <c r="BT2" s="86"/>
-      <c r="BW2" s="86"/>
-      <c r="BY2" s="86"/>
-      <c r="BZ2" s="86"/>
-      <c r="CB2" s="88"/>
-      <c r="CC2" s="86"/>
-      <c r="CE2" s="88"/>
-      <c r="CF2" s="86"/>
-      <c r="CH2" s="88"/>
-      <c r="CI2" s="86"/>
-      <c r="CK2" s="88"/>
-      <c r="CL2" s="86"/>
-      <c r="CN2" s="88"/>
-      <c r="CO2" s="86"/>
-      <c r="CQ2" s="88"/>
-      <c r="CR2" s="86"/>
-      <c r="CT2" s="88"/>
-      <c r="CU2" s="86"/>
+      <c r="AO2" s="81"/>
+      <c r="AP2" s="81"/>
+      <c r="AS2" s="81"/>
+      <c r="AV2" s="81"/>
+      <c r="AY2" s="81"/>
+      <c r="BB2" s="81"/>
+      <c r="BE2" s="81"/>
+      <c r="BH2" s="81"/>
+      <c r="BK2" s="81"/>
+      <c r="BN2" s="81"/>
+      <c r="BQ2" s="81"/>
+      <c r="BS2" s="53"/>
+      <c r="BT2" s="81"/>
+      <c r="BW2" s="81"/>
+      <c r="BY2" s="81"/>
+      <c r="BZ2" s="81"/>
+      <c r="CB2" s="82"/>
+      <c r="CC2" s="81"/>
+      <c r="CE2" s="82"/>
+      <c r="CF2" s="81"/>
+      <c r="CH2" s="82"/>
+      <c r="CI2" s="81"/>
+      <c r="CK2" s="82"/>
+      <c r="CL2" s="81"/>
+      <c r="CN2" s="82"/>
+      <c r="CO2" s="81"/>
+      <c r="CQ2" s="82"/>
+      <c r="CR2" s="81"/>
+      <c r="CT2" s="82"/>
+      <c r="CU2" s="81"/>
     </row>
     <row r="3" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="74" t="str">
+      <c r="E3" s="72" t="str">
         <f t="shared" ref="E3:E22" si="1">C3&amp;""&amp;D3</f>
         <v/>
       </c>
@@ -6870,38 +7329,38 @@
       <c r="AJ3" s="30"/>
       <c r="AK3" s="31"/>
       <c r="AL3" s="34"/>
-      <c r="AM3" s="55" t="str">
+      <c r="AM3" s="54" t="str">
         <f t="shared" ref="AM3:AM22" si="4">IF(AK3=0,"NA",AL3-$AC3)</f>
         <v>NA</v>
       </c>
-      <c r="AP3" s="86"/>
-      <c r="AS3" s="86"/>
-      <c r="AV3" s="86"/>
-      <c r="AY3" s="86"/>
-      <c r="BB3" s="86"/>
-      <c r="BE3" s="86"/>
-      <c r="BH3" s="86"/>
-      <c r="BK3" s="86"/>
-      <c r="BN3" s="86"/>
-      <c r="BQ3" s="86"/>
-      <c r="BT3" s="86"/>
-      <c r="BW3" s="86"/>
-      <c r="BY3" s="86"/>
-      <c r="BZ3" s="86"/>
-      <c r="CC3" s="86"/>
-      <c r="CF3" s="86"/>
-      <c r="CI3" s="86"/>
-      <c r="CL3" s="86"/>
-      <c r="CO3" s="86"/>
-      <c r="CR3" s="86"/>
-      <c r="CU3" s="86"/>
+      <c r="AP3" s="81"/>
+      <c r="AS3" s="81"/>
+      <c r="AV3" s="81"/>
+      <c r="AY3" s="81"/>
+      <c r="BB3" s="81"/>
+      <c r="BE3" s="81"/>
+      <c r="BH3" s="81"/>
+      <c r="BK3" s="81"/>
+      <c r="BN3" s="81"/>
+      <c r="BQ3" s="81"/>
+      <c r="BT3" s="81"/>
+      <c r="BW3" s="81"/>
+      <c r="BY3" s="81"/>
+      <c r="BZ3" s="81"/>
+      <c r="CC3" s="81"/>
+      <c r="CF3" s="81"/>
+      <c r="CI3" s="81"/>
+      <c r="CL3" s="81"/>
+      <c r="CO3" s="81"/>
+      <c r="CR3" s="81"/>
+      <c r="CU3" s="81"/>
     </row>
     <row r="4" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="74" t="str">
+      <c r="E4" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6953,47 +7412,47 @@
       <c r="AJ4" s="30"/>
       <c r="AK4" s="31"/>
       <c r="AL4" s="34"/>
-      <c r="AM4" s="55" t="str">
+      <c r="AM4" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP4" s="86"/>
-      <c r="AS4" s="86"/>
-      <c r="AV4" s="86"/>
-      <c r="AY4" s="86"/>
-      <c r="BB4" s="86"/>
-      <c r="BE4" s="86"/>
-      <c r="BG4" s="88"/>
-      <c r="BH4" s="86"/>
-      <c r="BJ4" s="88"/>
-      <c r="BK4" s="86"/>
-      <c r="BN4" s="86"/>
-      <c r="BQ4" s="86"/>
-      <c r="BT4" s="86"/>
-      <c r="BW4" s="86"/>
-      <c r="BY4" s="86"/>
-      <c r="BZ4" s="86"/>
-      <c r="CB4" s="88"/>
-      <c r="CC4" s="86"/>
-      <c r="CE4" s="88"/>
-      <c r="CF4" s="86"/>
-      <c r="CH4" s="88"/>
-      <c r="CI4" s="86"/>
-      <c r="CK4" s="88"/>
-      <c r="CL4" s="86"/>
-      <c r="CN4" s="88"/>
-      <c r="CO4" s="86"/>
-      <c r="CQ4" s="88"/>
-      <c r="CR4" s="86"/>
-      <c r="CT4" s="88"/>
-      <c r="CU4" s="86"/>
+      <c r="AP4" s="81"/>
+      <c r="AS4" s="81"/>
+      <c r="AV4" s="81"/>
+      <c r="AY4" s="81"/>
+      <c r="BB4" s="81"/>
+      <c r="BE4" s="81"/>
+      <c r="BG4" s="82"/>
+      <c r="BH4" s="81"/>
+      <c r="BJ4" s="82"/>
+      <c r="BK4" s="81"/>
+      <c r="BN4" s="81"/>
+      <c r="BQ4" s="81"/>
+      <c r="BT4" s="81"/>
+      <c r="BW4" s="81"/>
+      <c r="BY4" s="81"/>
+      <c r="BZ4" s="81"/>
+      <c r="CB4" s="82"/>
+      <c r="CC4" s="81"/>
+      <c r="CE4" s="82"/>
+      <c r="CF4" s="81"/>
+      <c r="CH4" s="82"/>
+      <c r="CI4" s="81"/>
+      <c r="CK4" s="82"/>
+      <c r="CL4" s="81"/>
+      <c r="CN4" s="82"/>
+      <c r="CO4" s="81"/>
+      <c r="CQ4" s="82"/>
+      <c r="CR4" s="81"/>
+      <c r="CT4" s="82"/>
+      <c r="CU4" s="81"/>
     </row>
     <row r="5" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="74" t="str">
+      <c r="E5" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7045,38 +7504,38 @@
       <c r="AJ5" s="30"/>
       <c r="AK5" s="31"/>
       <c r="AL5" s="34"/>
-      <c r="AM5" s="55" t="str">
+      <c r="AM5" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP5" s="86"/>
-      <c r="AS5" s="86"/>
-      <c r="AV5" s="86"/>
-      <c r="AY5" s="86"/>
-      <c r="BB5" s="86"/>
-      <c r="BE5" s="86"/>
-      <c r="BH5" s="86"/>
-      <c r="BK5" s="86"/>
-      <c r="BN5" s="86"/>
-      <c r="BQ5" s="86"/>
-      <c r="BT5" s="86"/>
-      <c r="BW5" s="86"/>
-      <c r="BY5" s="86"/>
-      <c r="BZ5" s="86"/>
-      <c r="CC5" s="86"/>
-      <c r="CF5" s="86"/>
-      <c r="CI5" s="86"/>
-      <c r="CL5" s="86"/>
-      <c r="CO5" s="86"/>
-      <c r="CR5" s="86"/>
-      <c r="CU5" s="86"/>
+      <c r="AP5" s="81"/>
+      <c r="AS5" s="81"/>
+      <c r="AV5" s="81"/>
+      <c r="AY5" s="81"/>
+      <c r="BB5" s="81"/>
+      <c r="BE5" s="81"/>
+      <c r="BH5" s="81"/>
+      <c r="BK5" s="81"/>
+      <c r="BN5" s="81"/>
+      <c r="BQ5" s="81"/>
+      <c r="BT5" s="81"/>
+      <c r="BW5" s="81"/>
+      <c r="BY5" s="81"/>
+      <c r="BZ5" s="81"/>
+      <c r="CC5" s="81"/>
+      <c r="CF5" s="81"/>
+      <c r="CI5" s="81"/>
+      <c r="CL5" s="81"/>
+      <c r="CO5" s="81"/>
+      <c r="CR5" s="81"/>
+      <c r="CU5" s="81"/>
     </row>
     <row r="6" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="74" t="str">
+      <c r="E6" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7128,38 +7587,38 @@
       <c r="AJ6" s="30"/>
       <c r="AK6" s="31"/>
       <c r="AL6" s="34"/>
-      <c r="AM6" s="55" t="str">
+      <c r="AM6" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP6" s="86"/>
-      <c r="AS6" s="86"/>
-      <c r="AV6" s="86"/>
-      <c r="AY6" s="86"/>
-      <c r="BB6" s="86"/>
-      <c r="BE6" s="86"/>
-      <c r="BH6" s="86"/>
-      <c r="BK6" s="86"/>
-      <c r="BN6" s="86"/>
-      <c r="BQ6" s="86"/>
-      <c r="BT6" s="86"/>
-      <c r="BW6" s="86"/>
-      <c r="BY6" s="86"/>
-      <c r="BZ6" s="86"/>
-      <c r="CC6" s="86"/>
-      <c r="CF6" s="86"/>
-      <c r="CI6" s="86"/>
-      <c r="CL6" s="86"/>
-      <c r="CO6" s="86"/>
-      <c r="CR6" s="86"/>
-      <c r="CU6" s="86"/>
+      <c r="AP6" s="81"/>
+      <c r="AS6" s="81"/>
+      <c r="AV6" s="81"/>
+      <c r="AY6" s="81"/>
+      <c r="BB6" s="81"/>
+      <c r="BE6" s="81"/>
+      <c r="BH6" s="81"/>
+      <c r="BK6" s="81"/>
+      <c r="BN6" s="81"/>
+      <c r="BQ6" s="81"/>
+      <c r="BT6" s="81"/>
+      <c r="BW6" s="81"/>
+      <c r="BY6" s="81"/>
+      <c r="BZ6" s="81"/>
+      <c r="CC6" s="81"/>
+      <c r="CF6" s="81"/>
+      <c r="CI6" s="81"/>
+      <c r="CL6" s="81"/>
+      <c r="CO6" s="81"/>
+      <c r="CR6" s="81"/>
+      <c r="CU6" s="81"/>
     </row>
     <row r="7" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="74" t="str">
+      <c r="E7" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7211,38 +7670,38 @@
       <c r="AJ7" s="30"/>
       <c r="AK7" s="31"/>
       <c r="AL7" s="34"/>
-      <c r="AM7" s="55" t="str">
+      <c r="AM7" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP7" s="86"/>
-      <c r="AS7" s="86"/>
-      <c r="AV7" s="86"/>
-      <c r="AY7" s="86"/>
-      <c r="BB7" s="86"/>
-      <c r="BE7" s="86"/>
-      <c r="BH7" s="86"/>
-      <c r="BK7" s="86"/>
-      <c r="BN7" s="86"/>
-      <c r="BQ7" s="86"/>
-      <c r="BT7" s="86"/>
-      <c r="BW7" s="86"/>
-      <c r="BY7" s="86"/>
-      <c r="BZ7" s="86"/>
-      <c r="CC7" s="86"/>
-      <c r="CF7" s="86"/>
-      <c r="CI7" s="86"/>
-      <c r="CL7" s="86"/>
-      <c r="CO7" s="86"/>
-      <c r="CR7" s="86"/>
-      <c r="CU7" s="86"/>
+      <c r="AP7" s="81"/>
+      <c r="AS7" s="81"/>
+      <c r="AV7" s="81"/>
+      <c r="AY7" s="81"/>
+      <c r="BB7" s="81"/>
+      <c r="BE7" s="81"/>
+      <c r="BH7" s="81"/>
+      <c r="BK7" s="81"/>
+      <c r="BN7" s="81"/>
+      <c r="BQ7" s="81"/>
+      <c r="BT7" s="81"/>
+      <c r="BW7" s="81"/>
+      <c r="BY7" s="81"/>
+      <c r="BZ7" s="81"/>
+      <c r="CC7" s="81"/>
+      <c r="CF7" s="81"/>
+      <c r="CI7" s="81"/>
+      <c r="CL7" s="81"/>
+      <c r="CO7" s="81"/>
+      <c r="CR7" s="81"/>
+      <c r="CU7" s="81"/>
     </row>
     <row r="8" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="74" t="str">
+      <c r="E8" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7294,41 +7753,41 @@
       <c r="AJ8" s="30"/>
       <c r="AK8" s="31"/>
       <c r="AL8" s="34"/>
-      <c r="AM8" s="55" t="str">
+      <c r="AM8" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO8" s="87"/>
-      <c r="AP8" s="86"/>
-      <c r="AS8" s="86"/>
-      <c r="AV8" s="86"/>
-      <c r="AY8" s="86"/>
-      <c r="BB8" s="86"/>
-      <c r="BE8" s="86"/>
-      <c r="BH8" s="86"/>
-      <c r="BK8" s="86"/>
-      <c r="BN8" s="86"/>
-      <c r="BQ8" s="86"/>
-      <c r="BT8" s="86"/>
-      <c r="BW8" s="86"/>
-      <c r="BY8" s="86"/>
-      <c r="BZ8" s="86"/>
-      <c r="CC8" s="86"/>
-      <c r="CF8" s="86"/>
-      <c r="CI8" s="86"/>
-      <c r="CL8" s="86"/>
-      <c r="CO8" s="86"/>
-      <c r="CQ8" s="87"/>
-      <c r="CR8" s="86"/>
-      <c r="CT8" s="87"/>
-      <c r="CU8" s="86"/>
+      <c r="AO8" s="53"/>
+      <c r="AP8" s="81"/>
+      <c r="AS8" s="81"/>
+      <c r="AV8" s="81"/>
+      <c r="AY8" s="81"/>
+      <c r="BB8" s="81"/>
+      <c r="BE8" s="81"/>
+      <c r="BH8" s="81"/>
+      <c r="BK8" s="81"/>
+      <c r="BN8" s="81"/>
+      <c r="BQ8" s="81"/>
+      <c r="BT8" s="81"/>
+      <c r="BW8" s="81"/>
+      <c r="BY8" s="81"/>
+      <c r="BZ8" s="81"/>
+      <c r="CC8" s="81"/>
+      <c r="CF8" s="81"/>
+      <c r="CI8" s="81"/>
+      <c r="CL8" s="81"/>
+      <c r="CO8" s="81"/>
+      <c r="CQ8" s="53"/>
+      <c r="CR8" s="81"/>
+      <c r="CT8" s="53"/>
+      <c r="CU8" s="81"/>
     </row>
     <row r="9" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="74" t="str">
+      <c r="E9" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7380,41 +7839,41 @@
       <c r="AJ9" s="30"/>
       <c r="AK9" s="31"/>
       <c r="AL9" s="34"/>
-      <c r="AM9" s="55" t="str">
+      <c r="AM9" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP9" s="86"/>
-      <c r="AS9" s="86"/>
-      <c r="AV9" s="86"/>
-      <c r="AY9" s="86"/>
-      <c r="BB9" s="86"/>
-      <c r="BE9" s="86"/>
-      <c r="BH9" s="86"/>
-      <c r="BJ9" s="88"/>
-      <c r="BK9" s="86"/>
-      <c r="BN9" s="86"/>
-      <c r="BQ9" s="86"/>
-      <c r="BT9" s="86"/>
-      <c r="BW9" s="86"/>
-      <c r="BY9" s="86"/>
-      <c r="BZ9" s="86"/>
-      <c r="CC9" s="86"/>
-      <c r="CF9" s="86"/>
-      <c r="CI9" s="86"/>
-      <c r="CL9" s="86"/>
-      <c r="CO9" s="86"/>
-      <c r="CQ9" s="86"/>
-      <c r="CR9" s="86"/>
-      <c r="CT9" s="86"/>
-      <c r="CU9" s="86"/>
+      <c r="AP9" s="81"/>
+      <c r="AS9" s="81"/>
+      <c r="AV9" s="81"/>
+      <c r="AY9" s="81"/>
+      <c r="BB9" s="81"/>
+      <c r="BE9" s="81"/>
+      <c r="BH9" s="81"/>
+      <c r="BJ9" s="82"/>
+      <c r="BK9" s="81"/>
+      <c r="BN9" s="81"/>
+      <c r="BQ9" s="81"/>
+      <c r="BT9" s="81"/>
+      <c r="BW9" s="81"/>
+      <c r="BY9" s="81"/>
+      <c r="BZ9" s="81"/>
+      <c r="CC9" s="81"/>
+      <c r="CF9" s="81"/>
+      <c r="CI9" s="81"/>
+      <c r="CL9" s="81"/>
+      <c r="CO9" s="81"/>
+      <c r="CQ9" s="81"/>
+      <c r="CR9" s="81"/>
+      <c r="CT9" s="81"/>
+      <c r="CU9" s="81"/>
     </row>
     <row r="10" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="74" t="str">
+      <c r="E10" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7466,46 +7925,46 @@
       <c r="AJ10" s="30"/>
       <c r="AK10" s="31"/>
       <c r="AL10" s="34"/>
-      <c r="AM10" s="55" t="str">
+      <c r="AM10" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO10" s="88"/>
-      <c r="AP10" s="86"/>
-      <c r="AS10" s="86"/>
-      <c r="AV10" s="86"/>
-      <c r="AY10" s="86"/>
-      <c r="BB10" s="86"/>
-      <c r="BE10" s="86"/>
-      <c r="BH10" s="86"/>
-      <c r="BK10" s="86"/>
-      <c r="BN10" s="86"/>
-      <c r="BQ10" s="86"/>
-      <c r="BT10" s="86"/>
-      <c r="BW10" s="86"/>
-      <c r="BY10" s="86"/>
-      <c r="BZ10" s="86"/>
-      <c r="CB10" s="88"/>
-      <c r="CC10" s="86"/>
-      <c r="CE10" s="88"/>
-      <c r="CF10" s="86"/>
-      <c r="CH10" s="88"/>
-      <c r="CI10" s="86"/>
-      <c r="CK10" s="88"/>
-      <c r="CL10" s="86"/>
-      <c r="CN10" s="88"/>
-      <c r="CO10" s="86"/>
-      <c r="CQ10" s="88"/>
-      <c r="CR10" s="86"/>
-      <c r="CT10" s="88"/>
-      <c r="CU10" s="86"/>
+      <c r="AO10" s="82"/>
+      <c r="AP10" s="81"/>
+      <c r="AS10" s="81"/>
+      <c r="AV10" s="81"/>
+      <c r="AY10" s="81"/>
+      <c r="BB10" s="81"/>
+      <c r="BE10" s="81"/>
+      <c r="BH10" s="81"/>
+      <c r="BK10" s="81"/>
+      <c r="BN10" s="81"/>
+      <c r="BQ10" s="81"/>
+      <c r="BT10" s="81"/>
+      <c r="BW10" s="81"/>
+      <c r="BY10" s="81"/>
+      <c r="BZ10" s="81"/>
+      <c r="CB10" s="82"/>
+      <c r="CC10" s="81"/>
+      <c r="CE10" s="82"/>
+      <c r="CF10" s="81"/>
+      <c r="CH10" s="82"/>
+      <c r="CI10" s="81"/>
+      <c r="CK10" s="82"/>
+      <c r="CL10" s="81"/>
+      <c r="CN10" s="82"/>
+      <c r="CO10" s="81"/>
+      <c r="CQ10" s="82"/>
+      <c r="CR10" s="81"/>
+      <c r="CT10" s="82"/>
+      <c r="CU10" s="81"/>
     </row>
     <row r="11" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="74" t="str">
+      <c r="E11" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7557,50 +8016,50 @@
       <c r="AJ11" s="30"/>
       <c r="AK11" s="31"/>
       <c r="AL11" s="34"/>
-      <c r="AM11" s="55" t="str">
+      <c r="AM11" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO11" s="88"/>
-      <c r="AP11" s="86"/>
-      <c r="AS11" s="86"/>
-      <c r="AV11" s="86"/>
-      <c r="AX11" s="88"/>
-      <c r="AY11" s="86"/>
-      <c r="BA11" s="88"/>
-      <c r="BB11" s="86"/>
-      <c r="BE11" s="86"/>
-      <c r="BG11" s="88"/>
-      <c r="BH11" s="86"/>
-      <c r="BK11" s="86"/>
-      <c r="BM11" s="88"/>
-      <c r="BN11" s="86"/>
-      <c r="BQ11" s="86"/>
-      <c r="BT11" s="86"/>
-      <c r="BW11" s="86"/>
-      <c r="BY11" s="86"/>
-      <c r="BZ11" s="86"/>
-      <c r="CB11" s="88"/>
-      <c r="CC11" s="86"/>
-      <c r="CE11" s="88"/>
-      <c r="CF11" s="86"/>
-      <c r="CH11" s="88"/>
-      <c r="CI11" s="86"/>
-      <c r="CK11" s="88"/>
-      <c r="CL11" s="86"/>
-      <c r="CN11" s="88"/>
-      <c r="CO11" s="86"/>
-      <c r="CQ11" s="88"/>
-      <c r="CR11" s="86"/>
-      <c r="CT11" s="88"/>
-      <c r="CU11" s="86"/>
+      <c r="AO11" s="82"/>
+      <c r="AP11" s="81"/>
+      <c r="AS11" s="81"/>
+      <c r="AV11" s="81"/>
+      <c r="AX11" s="82"/>
+      <c r="AY11" s="81"/>
+      <c r="BA11" s="82"/>
+      <c r="BB11" s="81"/>
+      <c r="BE11" s="81"/>
+      <c r="BG11" s="82"/>
+      <c r="BH11" s="81"/>
+      <c r="BK11" s="81"/>
+      <c r="BM11" s="82"/>
+      <c r="BN11" s="81"/>
+      <c r="BQ11" s="81"/>
+      <c r="BT11" s="81"/>
+      <c r="BW11" s="81"/>
+      <c r="BY11" s="81"/>
+      <c r="BZ11" s="81"/>
+      <c r="CB11" s="82"/>
+      <c r="CC11" s="81"/>
+      <c r="CE11" s="82"/>
+      <c r="CF11" s="81"/>
+      <c r="CH11" s="82"/>
+      <c r="CI11" s="81"/>
+      <c r="CK11" s="82"/>
+      <c r="CL11" s="81"/>
+      <c r="CN11" s="82"/>
+      <c r="CO11" s="81"/>
+      <c r="CQ11" s="82"/>
+      <c r="CR11" s="81"/>
+      <c r="CT11" s="82"/>
+      <c r="CU11" s="81"/>
     </row>
     <row r="12" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="74" t="str">
+      <c r="E12" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7652,45 +8111,45 @@
       <c r="AJ12" s="30"/>
       <c r="AK12" s="31"/>
       <c r="AL12" s="34"/>
-      <c r="AM12" s="55" t="str">
+      <c r="AM12" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP12" s="86"/>
-      <c r="AS12" s="86"/>
-      <c r="AV12" s="86"/>
-      <c r="AY12" s="86"/>
-      <c r="BB12" s="86"/>
-      <c r="BE12" s="86"/>
-      <c r="BH12" s="86"/>
-      <c r="BK12" s="86"/>
-      <c r="BN12" s="86"/>
-      <c r="BQ12" s="86"/>
-      <c r="BT12" s="86"/>
-      <c r="BW12" s="86"/>
-      <c r="BY12" s="86"/>
-      <c r="BZ12" s="86"/>
-      <c r="CB12" s="87"/>
-      <c r="CC12" s="86"/>
-      <c r="CE12" s="87"/>
-      <c r="CF12" s="86"/>
-      <c r="CH12" s="87"/>
-      <c r="CI12" s="86"/>
-      <c r="CK12" s="87"/>
-      <c r="CL12" s="86"/>
-      <c r="CN12" s="87"/>
-      <c r="CO12" s="86"/>
-      <c r="CQ12" s="87"/>
-      <c r="CR12" s="86"/>
-      <c r="CT12" s="87"/>
-      <c r="CU12" s="86"/>
+      <c r="AP12" s="81"/>
+      <c r="AS12" s="81"/>
+      <c r="AV12" s="81"/>
+      <c r="AY12" s="81"/>
+      <c r="BB12" s="81"/>
+      <c r="BE12" s="81"/>
+      <c r="BH12" s="81"/>
+      <c r="BK12" s="81"/>
+      <c r="BN12" s="81"/>
+      <c r="BQ12" s="81"/>
+      <c r="BT12" s="81"/>
+      <c r="BW12" s="81"/>
+      <c r="BY12" s="81"/>
+      <c r="BZ12" s="81"/>
+      <c r="CB12" s="53"/>
+      <c r="CC12" s="81"/>
+      <c r="CE12" s="53"/>
+      <c r="CF12" s="81"/>
+      <c r="CH12" s="53"/>
+      <c r="CI12" s="81"/>
+      <c r="CK12" s="53"/>
+      <c r="CL12" s="81"/>
+      <c r="CN12" s="53"/>
+      <c r="CO12" s="81"/>
+      <c r="CQ12" s="53"/>
+      <c r="CR12" s="81"/>
+      <c r="CT12" s="53"/>
+      <c r="CU12" s="81"/>
     </row>
     <row r="13" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="74" t="str">
+      <c r="E13" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7742,42 +8201,42 @@
       <c r="AJ13" s="30"/>
       <c r="AK13" s="31"/>
       <c r="AL13" s="34"/>
-      <c r="AM13" s="55" t="str">
+      <c r="AM13" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP13" s="86"/>
-      <c r="AS13" s="86"/>
-      <c r="AV13" s="86"/>
-      <c r="AY13" s="86"/>
-      <c r="BB13" s="86"/>
-      <c r="BE13" s="86"/>
-      <c r="BG13" s="88"/>
-      <c r="BH13" s="86"/>
-      <c r="BK13" s="86"/>
-      <c r="BN13" s="86"/>
-      <c r="BQ13" s="86"/>
-      <c r="BS13" s="88"/>
-      <c r="BT13" s="86"/>
-      <c r="BW13" s="86"/>
-      <c r="BY13" s="86"/>
-      <c r="BZ13" s="86"/>
-      <c r="CC13" s="86"/>
-      <c r="CF13" s="86"/>
-      <c r="CI13" s="86"/>
-      <c r="CK13" s="88"/>
-      <c r="CL13" s="86"/>
-      <c r="CN13" s="88"/>
-      <c r="CO13" s="86"/>
-      <c r="CR13" s="86"/>
-      <c r="CU13" s="86"/>
+      <c r="AP13" s="81"/>
+      <c r="AS13" s="81"/>
+      <c r="AV13" s="81"/>
+      <c r="AY13" s="81"/>
+      <c r="BB13" s="81"/>
+      <c r="BE13" s="81"/>
+      <c r="BG13" s="82"/>
+      <c r="BH13" s="81"/>
+      <c r="BK13" s="81"/>
+      <c r="BN13" s="81"/>
+      <c r="BQ13" s="81"/>
+      <c r="BS13" s="82"/>
+      <c r="BT13" s="81"/>
+      <c r="BW13" s="81"/>
+      <c r="BY13" s="81"/>
+      <c r="BZ13" s="81"/>
+      <c r="CC13" s="81"/>
+      <c r="CF13" s="81"/>
+      <c r="CI13" s="81"/>
+      <c r="CK13" s="82"/>
+      <c r="CL13" s="81"/>
+      <c r="CN13" s="82"/>
+      <c r="CO13" s="81"/>
+      <c r="CR13" s="81"/>
+      <c r="CU13" s="81"/>
     </row>
     <row r="14" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="74" t="str">
+      <c r="E14" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7829,44 +8288,44 @@
       <c r="AJ14" s="30"/>
       <c r="AK14" s="31"/>
       <c r="AL14" s="32"/>
-      <c r="AM14" s="55" t="str">
+      <c r="AM14" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP14" s="86"/>
-      <c r="AS14" s="86"/>
-      <c r="AV14" s="86"/>
-      <c r="AX14" s="88"/>
-      <c r="AY14" s="86"/>
-      <c r="BA14" s="88"/>
-      <c r="BB14" s="86"/>
-      <c r="BE14" s="86"/>
-      <c r="BG14" s="88"/>
-      <c r="BH14" s="86"/>
-      <c r="BJ14" s="88"/>
-      <c r="BK14" s="86"/>
-      <c r="BN14" s="86"/>
-      <c r="BQ14" s="86"/>
-      <c r="BS14" s="88"/>
-      <c r="BT14" s="86"/>
-      <c r="BV14" s="88"/>
-      <c r="BW14" s="86"/>
-      <c r="BY14" s="86"/>
-      <c r="BZ14" s="86"/>
-      <c r="CC14" s="86"/>
-      <c r="CF14" s="86"/>
-      <c r="CI14" s="86"/>
-      <c r="CL14" s="86"/>
-      <c r="CO14" s="86"/>
-      <c r="CR14" s="86"/>
-      <c r="CU14" s="86"/>
+      <c r="AP14" s="81"/>
+      <c r="AS14" s="81"/>
+      <c r="AV14" s="81"/>
+      <c r="AX14" s="82"/>
+      <c r="AY14" s="81"/>
+      <c r="BA14" s="82"/>
+      <c r="BB14" s="81"/>
+      <c r="BE14" s="81"/>
+      <c r="BG14" s="82"/>
+      <c r="BH14" s="81"/>
+      <c r="BJ14" s="82"/>
+      <c r="BK14" s="81"/>
+      <c r="BN14" s="81"/>
+      <c r="BQ14" s="81"/>
+      <c r="BS14" s="82"/>
+      <c r="BT14" s="81"/>
+      <c r="BV14" s="82"/>
+      <c r="BW14" s="81"/>
+      <c r="BY14" s="81"/>
+      <c r="BZ14" s="81"/>
+      <c r="CC14" s="81"/>
+      <c r="CF14" s="81"/>
+      <c r="CI14" s="81"/>
+      <c r="CL14" s="81"/>
+      <c r="CO14" s="81"/>
+      <c r="CR14" s="81"/>
+      <c r="CU14" s="81"/>
     </row>
     <row r="15" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="74" t="str">
+      <c r="E15" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7918,43 +8377,43 @@
       <c r="AJ15" s="30"/>
       <c r="AK15" s="31"/>
       <c r="AL15" s="34"/>
-      <c r="AM15" s="55" t="str">
+      <c r="AM15" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP15" s="86"/>
-      <c r="AS15" s="86"/>
-      <c r="AV15" s="86"/>
-      <c r="AY15" s="86"/>
-      <c r="BB15" s="86"/>
-      <c r="BE15" s="86"/>
-      <c r="BG15" s="88"/>
-      <c r="BH15" s="86"/>
-      <c r="BK15" s="86"/>
-      <c r="BN15" s="86"/>
-      <c r="BQ15" s="86"/>
-      <c r="BS15" s="88"/>
-      <c r="BT15" s="86"/>
-      <c r="BV15" s="87"/>
-      <c r="BW15" s="86"/>
-      <c r="BY15" s="86"/>
-      <c r="BZ15" s="86"/>
-      <c r="CB15" s="87"/>
-      <c r="CC15" s="86"/>
-      <c r="CE15" s="87"/>
-      <c r="CF15" s="86"/>
-      <c r="CI15" s="86"/>
-      <c r="CL15" s="86"/>
-      <c r="CO15" s="86"/>
-      <c r="CR15" s="86"/>
-      <c r="CU15" s="86"/>
+      <c r="AP15" s="81"/>
+      <c r="AS15" s="81"/>
+      <c r="AV15" s="81"/>
+      <c r="AY15" s="81"/>
+      <c r="BB15" s="81"/>
+      <c r="BE15" s="81"/>
+      <c r="BG15" s="82"/>
+      <c r="BH15" s="81"/>
+      <c r="BK15" s="81"/>
+      <c r="BN15" s="81"/>
+      <c r="BQ15" s="81"/>
+      <c r="BS15" s="82"/>
+      <c r="BT15" s="81"/>
+      <c r="BV15" s="53"/>
+      <c r="BW15" s="81"/>
+      <c r="BY15" s="81"/>
+      <c r="BZ15" s="81"/>
+      <c r="CB15" s="53"/>
+      <c r="CC15" s="81"/>
+      <c r="CE15" s="53"/>
+      <c r="CF15" s="81"/>
+      <c r="CI15" s="81"/>
+      <c r="CL15" s="81"/>
+      <c r="CO15" s="81"/>
+      <c r="CR15" s="81"/>
+      <c r="CU15" s="81"/>
     </row>
     <row r="16" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="74" t="str">
+      <c r="E16" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8006,55 +8465,54 @@
       <c r="AJ16" s="30"/>
       <c r="AK16" s="31"/>
       <c r="AL16" s="34"/>
-      <c r="AM16" s="55" t="str">
+      <c r="AM16" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO16" s="88"/>
-      <c r="AP16" s="86"/>
-      <c r="AR16" s="88"/>
-      <c r="AS16" s="86"/>
-      <c r="AU16" s="88"/>
-      <c r="AV16" s="86"/>
-      <c r="AX16" s="88"/>
-      <c r="AY16" s="86"/>
-      <c r="BA16" s="88"/>
-      <c r="BB16" s="86"/>
-      <c r="BD16" s="88"/>
-      <c r="BE16" s="86"/>
-      <c r="BG16" s="88"/>
-      <c r="BH16" s="86"/>
-      <c r="BI16" s="85"/>
-      <c r="BJ16" s="88"/>
-      <c r="BK16" s="86"/>
-      <c r="BN16" s="86"/>
-      <c r="BQ16" s="86"/>
-      <c r="BS16" s="86"/>
-      <c r="BT16" s="86"/>
-      <c r="BW16" s="86"/>
-      <c r="BY16" s="86"/>
-      <c r="BZ16" s="86"/>
-      <c r="CB16" s="88"/>
-      <c r="CC16" s="86"/>
-      <c r="CE16" s="88"/>
-      <c r="CF16" s="86"/>
-      <c r="CH16" s="88"/>
-      <c r="CI16" s="86"/>
-      <c r="CK16" s="88"/>
-      <c r="CL16" s="86"/>
-      <c r="CN16" s="88"/>
-      <c r="CO16" s="86"/>
-      <c r="CQ16" s="88"/>
-      <c r="CR16" s="86"/>
-      <c r="CT16" s="88"/>
-      <c r="CU16" s="86"/>
+      <c r="AO16" s="82"/>
+      <c r="AP16" s="81"/>
+      <c r="AR16" s="82"/>
+      <c r="AS16" s="81"/>
+      <c r="AU16" s="82"/>
+      <c r="AV16" s="81"/>
+      <c r="AX16" s="82"/>
+      <c r="AY16" s="81"/>
+      <c r="BA16" s="82"/>
+      <c r="BB16" s="81"/>
+      <c r="BD16" s="82"/>
+      <c r="BE16" s="81"/>
+      <c r="BG16" s="82"/>
+      <c r="BH16" s="81"/>
+      <c r="BJ16" s="82"/>
+      <c r="BK16" s="81"/>
+      <c r="BN16" s="81"/>
+      <c r="BQ16" s="81"/>
+      <c r="BS16" s="81"/>
+      <c r="BT16" s="81"/>
+      <c r="BW16" s="81"/>
+      <c r="BY16" s="81"/>
+      <c r="BZ16" s="81"/>
+      <c r="CB16" s="82"/>
+      <c r="CC16" s="81"/>
+      <c r="CE16" s="82"/>
+      <c r="CF16" s="81"/>
+      <c r="CH16" s="82"/>
+      <c r="CI16" s="81"/>
+      <c r="CK16" s="82"/>
+      <c r="CL16" s="81"/>
+      <c r="CN16" s="82"/>
+      <c r="CO16" s="81"/>
+      <c r="CQ16" s="82"/>
+      <c r="CR16" s="81"/>
+      <c r="CT16" s="82"/>
+      <c r="CU16" s="81"/>
     </row>
     <row r="17" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="74" t="str">
+      <c r="E17" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8106,58 +8564,55 @@
       <c r="AJ17" s="30"/>
       <c r="AK17" s="31"/>
       <c r="AL17" s="34"/>
-      <c r="AM17" s="55" t="str">
+      <c r="AM17" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO17" s="88"/>
-      <c r="AP17" s="86"/>
-      <c r="AR17" s="88"/>
-      <c r="AS17" s="86"/>
-      <c r="AU17" s="88"/>
-      <c r="AV17" s="86"/>
-      <c r="AX17" s="88"/>
-      <c r="AY17" s="86"/>
-      <c r="BA17" s="88"/>
-      <c r="BB17" s="86"/>
-      <c r="BD17" s="88"/>
-      <c r="BE17" s="86"/>
-      <c r="BG17" s="88"/>
-      <c r="BH17" s="86"/>
-      <c r="BI17" s="85"/>
-      <c r="BJ17" s="88"/>
-      <c r="BK17" s="86"/>
-      <c r="BL17" s="85"/>
-      <c r="BM17" s="88"/>
-      <c r="BN17" s="86"/>
-      <c r="BO17" s="85"/>
-      <c r="BP17" s="88"/>
-      <c r="BQ17" s="86"/>
-      <c r="BT17" s="86"/>
-      <c r="BW17" s="86"/>
-      <c r="BY17" s="86"/>
-      <c r="BZ17" s="86"/>
-      <c r="CB17" s="88"/>
-      <c r="CC17" s="86"/>
-      <c r="CE17" s="88"/>
-      <c r="CF17" s="86"/>
-      <c r="CH17" s="88"/>
-      <c r="CI17" s="86"/>
-      <c r="CK17" s="88"/>
-      <c r="CL17" s="86"/>
-      <c r="CN17" s="88"/>
-      <c r="CO17" s="86"/>
-      <c r="CQ17" s="88"/>
-      <c r="CR17" s="86"/>
-      <c r="CT17" s="88"/>
-      <c r="CU17" s="86"/>
+      <c r="AO17" s="82"/>
+      <c r="AP17" s="81"/>
+      <c r="AR17" s="82"/>
+      <c r="AS17" s="81"/>
+      <c r="AU17" s="82"/>
+      <c r="AV17" s="81"/>
+      <c r="AX17" s="82"/>
+      <c r="AY17" s="81"/>
+      <c r="BA17" s="82"/>
+      <c r="BB17" s="81"/>
+      <c r="BD17" s="82"/>
+      <c r="BE17" s="81"/>
+      <c r="BG17" s="82"/>
+      <c r="BH17" s="81"/>
+      <c r="BJ17" s="82"/>
+      <c r="BK17" s="81"/>
+      <c r="BM17" s="82"/>
+      <c r="BN17" s="81"/>
+      <c r="BP17" s="82"/>
+      <c r="BQ17" s="81"/>
+      <c r="BT17" s="81"/>
+      <c r="BW17" s="81"/>
+      <c r="BY17" s="81"/>
+      <c r="BZ17" s="81"/>
+      <c r="CB17" s="82"/>
+      <c r="CC17" s="81"/>
+      <c r="CE17" s="82"/>
+      <c r="CF17" s="81"/>
+      <c r="CH17" s="82"/>
+      <c r="CI17" s="81"/>
+      <c r="CK17" s="82"/>
+      <c r="CL17" s="81"/>
+      <c r="CN17" s="82"/>
+      <c r="CO17" s="81"/>
+      <c r="CQ17" s="82"/>
+      <c r="CR17" s="81"/>
+      <c r="CT17" s="82"/>
+      <c r="CU17" s="81"/>
     </row>
     <row r="18" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="74" t="str">
+      <c r="E18" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8209,55 +8664,55 @@
       <c r="AJ18" s="30"/>
       <c r="AK18" s="31"/>
       <c r="AL18" s="34"/>
-      <c r="AM18" s="55" t="str">
+      <c r="AM18" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO18" s="88"/>
-      <c r="AP18" s="86"/>
-      <c r="AR18" s="88"/>
-      <c r="AS18" s="86"/>
-      <c r="AU18" s="88"/>
-      <c r="AV18" s="86"/>
-      <c r="AX18" s="88"/>
-      <c r="AY18" s="86"/>
-      <c r="BA18" s="88"/>
-      <c r="BB18" s="86"/>
-      <c r="BD18" s="88"/>
-      <c r="BE18" s="86"/>
-      <c r="BG18" s="88"/>
-      <c r="BH18" s="86"/>
-      <c r="BJ18" s="88"/>
-      <c r="BK18" s="86"/>
-      <c r="BM18" s="88"/>
-      <c r="BN18" s="86"/>
-      <c r="BP18" s="88"/>
-      <c r="BQ18" s="86"/>
-      <c r="BT18" s="86"/>
-      <c r="BW18" s="86"/>
-      <c r="BY18" s="86"/>
-      <c r="BZ18" s="86"/>
-      <c r="CB18" s="88"/>
-      <c r="CC18" s="86"/>
-      <c r="CE18" s="88"/>
-      <c r="CF18" s="86"/>
-      <c r="CH18" s="88"/>
-      <c r="CI18" s="86"/>
-      <c r="CK18" s="88"/>
-      <c r="CL18" s="86"/>
-      <c r="CN18" s="88"/>
-      <c r="CO18" s="86"/>
-      <c r="CQ18" s="88"/>
-      <c r="CR18" s="86"/>
-      <c r="CT18" s="88"/>
-      <c r="CU18" s="86"/>
+      <c r="AO18" s="82"/>
+      <c r="AP18" s="81"/>
+      <c r="AR18" s="82"/>
+      <c r="AS18" s="81"/>
+      <c r="AU18" s="82"/>
+      <c r="AV18" s="81"/>
+      <c r="AX18" s="82"/>
+      <c r="AY18" s="81"/>
+      <c r="BA18" s="82"/>
+      <c r="BB18" s="81"/>
+      <c r="BD18" s="82"/>
+      <c r="BE18" s="81"/>
+      <c r="BG18" s="82"/>
+      <c r="BH18" s="81"/>
+      <c r="BJ18" s="82"/>
+      <c r="BK18" s="81"/>
+      <c r="BM18" s="82"/>
+      <c r="BN18" s="81"/>
+      <c r="BP18" s="82"/>
+      <c r="BQ18" s="81"/>
+      <c r="BT18" s="81"/>
+      <c r="BW18" s="81"/>
+      <c r="BY18" s="81"/>
+      <c r="BZ18" s="81"/>
+      <c r="CB18" s="82"/>
+      <c r="CC18" s="81"/>
+      <c r="CE18" s="82"/>
+      <c r="CF18" s="81"/>
+      <c r="CH18" s="82"/>
+      <c r="CI18" s="81"/>
+      <c r="CK18" s="82"/>
+      <c r="CL18" s="81"/>
+      <c r="CN18" s="82"/>
+      <c r="CO18" s="81"/>
+      <c r="CQ18" s="82"/>
+      <c r="CR18" s="81"/>
+      <c r="CT18" s="82"/>
+      <c r="CU18" s="81"/>
     </row>
     <row r="19" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="74" t="str">
+      <c r="E19" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8309,55 +8764,55 @@
       <c r="AJ19" s="30"/>
       <c r="AK19" s="31"/>
       <c r="AL19" s="34"/>
-      <c r="AM19" s="55" t="str">
+      <c r="AM19" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO19" s="88"/>
-      <c r="AP19" s="86"/>
-      <c r="AR19" s="88"/>
-      <c r="AS19" s="86"/>
-      <c r="AU19" s="88"/>
-      <c r="AV19" s="86"/>
-      <c r="AX19" s="88"/>
-      <c r="AY19" s="86"/>
-      <c r="BA19" s="88"/>
-      <c r="BB19" s="86"/>
-      <c r="BD19" s="88"/>
-      <c r="BE19" s="86"/>
-      <c r="BG19" s="88"/>
-      <c r="BH19" s="86"/>
-      <c r="BJ19" s="88"/>
-      <c r="BK19" s="86"/>
-      <c r="BM19" s="88"/>
-      <c r="BN19" s="86"/>
-      <c r="BP19" s="88"/>
-      <c r="BQ19" s="86"/>
-      <c r="BT19" s="86"/>
-      <c r="BW19" s="86"/>
-      <c r="BY19" s="86"/>
-      <c r="BZ19" s="86"/>
-      <c r="CB19" s="88"/>
-      <c r="CC19" s="86"/>
-      <c r="CE19" s="88"/>
-      <c r="CF19" s="86"/>
-      <c r="CH19" s="88"/>
-      <c r="CI19" s="86"/>
-      <c r="CK19" s="88"/>
-      <c r="CL19" s="86"/>
-      <c r="CN19" s="88"/>
-      <c r="CO19" s="86"/>
-      <c r="CQ19" s="88"/>
-      <c r="CR19" s="86"/>
-      <c r="CT19" s="88"/>
-      <c r="CU19" s="86"/>
+      <c r="AO19" s="82"/>
+      <c r="AP19" s="81"/>
+      <c r="AR19" s="82"/>
+      <c r="AS19" s="81"/>
+      <c r="AU19" s="82"/>
+      <c r="AV19" s="81"/>
+      <c r="AX19" s="82"/>
+      <c r="AY19" s="81"/>
+      <c r="BA19" s="82"/>
+      <c r="BB19" s="81"/>
+      <c r="BD19" s="82"/>
+      <c r="BE19" s="81"/>
+      <c r="BG19" s="82"/>
+      <c r="BH19" s="81"/>
+      <c r="BJ19" s="82"/>
+      <c r="BK19" s="81"/>
+      <c r="BM19" s="82"/>
+      <c r="BN19" s="81"/>
+      <c r="BP19" s="82"/>
+      <c r="BQ19" s="81"/>
+      <c r="BT19" s="81"/>
+      <c r="BW19" s="81"/>
+      <c r="BY19" s="81"/>
+      <c r="BZ19" s="81"/>
+      <c r="CB19" s="82"/>
+      <c r="CC19" s="81"/>
+      <c r="CE19" s="82"/>
+      <c r="CF19" s="81"/>
+      <c r="CH19" s="82"/>
+      <c r="CI19" s="81"/>
+      <c r="CK19" s="82"/>
+      <c r="CL19" s="81"/>
+      <c r="CN19" s="82"/>
+      <c r="CO19" s="81"/>
+      <c r="CQ19" s="82"/>
+      <c r="CR19" s="81"/>
+      <c r="CT19" s="82"/>
+      <c r="CU19" s="81"/>
     </row>
     <row r="20" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="74" t="str">
+      <c r="E20" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8409,57 +8864,57 @@
       <c r="AJ20" s="30"/>
       <c r="AK20" s="31"/>
       <c r="AL20" s="34"/>
-      <c r="AM20" s="55" t="str">
+      <c r="AM20" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO20" s="88"/>
-      <c r="AP20" s="86"/>
-      <c r="AR20" s="88"/>
-      <c r="AS20" s="86"/>
-      <c r="AU20" s="88"/>
-      <c r="AV20" s="86"/>
-      <c r="AX20" s="88"/>
-      <c r="AY20" s="86"/>
-      <c r="BA20" s="88"/>
-      <c r="BB20" s="86"/>
-      <c r="BD20" s="88"/>
-      <c r="BE20" s="86"/>
-      <c r="BG20" s="88"/>
-      <c r="BH20" s="86"/>
-      <c r="BJ20" s="88"/>
-      <c r="BK20" s="86"/>
-      <c r="BM20" s="88"/>
-      <c r="BN20" s="86"/>
-      <c r="BP20" s="88"/>
-      <c r="BQ20" s="86"/>
-      <c r="BS20" s="88"/>
-      <c r="BT20" s="86"/>
-      <c r="BV20" s="88"/>
-      <c r="BW20" s="86"/>
-      <c r="BY20" s="86"/>
-      <c r="BZ20" s="86"/>
-      <c r="CB20" s="88"/>
-      <c r="CC20" s="86"/>
-      <c r="CE20" s="88"/>
-      <c r="CF20" s="86"/>
-      <c r="CH20" s="88"/>
-      <c r="CI20" s="86"/>
-      <c r="CK20" s="88"/>
-      <c r="CL20" s="86"/>
-      <c r="CN20" s="88"/>
-      <c r="CO20" s="86"/>
-      <c r="CQ20" s="88"/>
-      <c r="CR20" s="86"/>
-      <c r="CT20" s="88"/>
-      <c r="CU20" s="86"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="81"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="81"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="81"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="81"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="81"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="81"/>
+      <c r="BG20" s="82"/>
+      <c r="BH20" s="81"/>
+      <c r="BJ20" s="82"/>
+      <c r="BK20" s="81"/>
+      <c r="BM20" s="82"/>
+      <c r="BN20" s="81"/>
+      <c r="BP20" s="82"/>
+      <c r="BQ20" s="81"/>
+      <c r="BS20" s="82"/>
+      <c r="BT20" s="81"/>
+      <c r="BV20" s="82"/>
+      <c r="BW20" s="81"/>
+      <c r="BY20" s="81"/>
+      <c r="BZ20" s="81"/>
+      <c r="CB20" s="82"/>
+      <c r="CC20" s="81"/>
+      <c r="CE20" s="82"/>
+      <c r="CF20" s="81"/>
+      <c r="CH20" s="82"/>
+      <c r="CI20" s="81"/>
+      <c r="CK20" s="82"/>
+      <c r="CL20" s="81"/>
+      <c r="CN20" s="82"/>
+      <c r="CO20" s="81"/>
+      <c r="CQ20" s="82"/>
+      <c r="CR20" s="81"/>
+      <c r="CT20" s="82"/>
+      <c r="CU20" s="81"/>
     </row>
     <row r="21" spans="1:99" x14ac:dyDescent="0.35">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="74" t="str">
+      <c r="E21" s="72" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8488,18 +8943,18 @@
       <c r="S21" s="5"/>
       <c r="T21" s="5"/>
       <c r="U21" s="8"/>
-      <c r="V21" s="76"/>
-      <c r="W21" s="77"/>
-      <c r="X21" s="77"/>
-      <c r="Y21" s="77"/>
-      <c r="Z21" s="77"/>
-      <c r="AA21" s="77"/>
+      <c r="V21" s="74"/>
+      <c r="W21" s="75"/>
+      <c r="X21" s="75"/>
+      <c r="Y21" s="75"/>
+      <c r="Z21" s="75"/>
+      <c r="AA21" s="75"/>
       <c r="AB21" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC21" s="78"/>
-      <c r="AD21" s="78"/>
+      <c r="AC21" s="76"/>
+      <c r="AD21" s="76"/>
       <c r="AE21" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8511,41 +8966,41 @@
       <c r="AJ21" s="30"/>
       <c r="AK21" s="31"/>
       <c r="AL21" s="32"/>
-      <c r="AM21" s="55" t="str">
+      <c r="AM21" s="54" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AP21" s="86"/>
-      <c r="AS21" s="86"/>
-      <c r="AV21" s="86"/>
-      <c r="AY21" s="86"/>
-      <c r="BA21" s="88"/>
-      <c r="BB21" s="86"/>
-      <c r="BE21" s="86"/>
-      <c r="BH21" s="86"/>
-      <c r="BJ21" s="86"/>
-      <c r="BK21" s="86"/>
-      <c r="BN21" s="86"/>
-      <c r="BQ21" s="86"/>
-      <c r="BT21" s="86"/>
-      <c r="BW21" s="86"/>
-      <c r="BY21" s="88"/>
-      <c r="BZ21" s="86"/>
-      <c r="CC21" s="86"/>
-      <c r="CF21" s="86"/>
-      <c r="CI21" s="86"/>
-      <c r="CL21" s="86"/>
-      <c r="CO21" s="86"/>
-      <c r="CR21" s="86"/>
-      <c r="CT21" s="86"/>
-      <c r="CU21" s="86"/>
+      <c r="AP21" s="81"/>
+      <c r="AS21" s="81"/>
+      <c r="AV21" s="81"/>
+      <c r="AY21" s="81"/>
+      <c r="BA21" s="82"/>
+      <c r="BB21" s="81"/>
+      <c r="BE21" s="81"/>
+      <c r="BH21" s="81"/>
+      <c r="BJ21" s="81"/>
+      <c r="BK21" s="81"/>
+      <c r="BN21" s="81"/>
+      <c r="BQ21" s="81"/>
+      <c r="BT21" s="81"/>
+      <c r="BW21" s="81"/>
+      <c r="BY21" s="82"/>
+      <c r="BZ21" s="81"/>
+      <c r="CC21" s="81"/>
+      <c r="CF21" s="81"/>
+      <c r="CI21" s="81"/>
+      <c r="CL21" s="81"/>
+      <c r="CO21" s="81"/>
+      <c r="CR21" s="81"/>
+      <c r="CT21" s="81"/>
+      <c r="CU21" s="81"/>
     </row>
     <row r="22" spans="1:99" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
-      <c r="E22" s="75" t="str">
+      <c r="E22" s="73" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8574,18 +9029,18 @@
       <c r="S22" s="11"/>
       <c r="T22" s="11"/>
       <c r="U22" s="14"/>
-      <c r="V22" s="79"/>
-      <c r="W22" s="68"/>
-      <c r="X22" s="68"/>
-      <c r="Y22" s="68"/>
-      <c r="Z22" s="68"/>
-      <c r="AA22" s="68"/>
+      <c r="V22" s="77"/>
+      <c r="W22" s="67"/>
+      <c r="X22" s="67"/>
+      <c r="Y22" s="67"/>
+      <c r="Z22" s="67"/>
+      <c r="AA22" s="67"/>
       <c r="AB22" s="23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC22" s="80"/>
-      <c r="AD22" s="80"/>
+      <c r="AC22" s="78"/>
+      <c r="AD22" s="78"/>
       <c r="AE22" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8597,35 +9052,35 @@
       <c r="AJ22" s="37"/>
       <c r="AK22" s="38"/>
       <c r="AL22" s="39"/>
-      <c r="AM22" s="83" t="str">
+      <c r="AM22" s="80" t="str">
         <f t="shared" si="4"/>
         <v>NA</v>
       </c>
-      <c r="AO22" s="88"/>
-      <c r="AP22" s="86"/>
-      <c r="AS22" s="86"/>
-      <c r="AV22" s="86"/>
-      <c r="AY22" s="86"/>
-      <c r="BA22" s="88"/>
-      <c r="BB22" s="86"/>
-      <c r="BE22" s="86"/>
-      <c r="BH22" s="86"/>
-      <c r="BJ22" s="88"/>
-      <c r="BK22" s="86"/>
-      <c r="BN22" s="86"/>
-      <c r="BQ22" s="86"/>
-      <c r="BT22" s="86"/>
-      <c r="BW22" s="86"/>
-      <c r="BZ22" s="86"/>
-      <c r="CC22" s="86"/>
-      <c r="CF22" s="86"/>
-      <c r="CI22" s="86"/>
-      <c r="CL22" s="86"/>
-      <c r="CO22" s="86"/>
-      <c r="CQ22" s="88"/>
-      <c r="CR22" s="86"/>
-      <c r="CT22" s="88"/>
-      <c r="CU22" s="86"/>
+      <c r="AO22" s="82"/>
+      <c r="AP22" s="81"/>
+      <c r="AS22" s="81"/>
+      <c r="AV22" s="81"/>
+      <c r="AY22" s="81"/>
+      <c r="BA22" s="82"/>
+      <c r="BB22" s="81"/>
+      <c r="BE22" s="81"/>
+      <c r="BH22" s="81"/>
+      <c r="BJ22" s="82"/>
+      <c r="BK22" s="81"/>
+      <c r="BN22" s="81"/>
+      <c r="BQ22" s="81"/>
+      <c r="BT22" s="81"/>
+      <c r="BW22" s="81"/>
+      <c r="BZ22" s="81"/>
+      <c r="CC22" s="81"/>
+      <c r="CF22" s="81"/>
+      <c r="CI22" s="81"/>
+      <c r="CL22" s="81"/>
+      <c r="CO22" s="81"/>
+      <c r="CQ22" s="82"/>
+      <c r="CR22" s="81"/>
+      <c r="CT22" s="82"/>
+      <c r="CU22" s="81"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8638,234 +9093,234 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="C1" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="60" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="63">
+      <c r="B2" s="62">
         <v>-5.4793240000000001</v>
       </c>
-      <c r="C2" s="63">
+      <c r="C2" s="62">
         <v>119.31157399999999</v>
       </c>
-      <c r="D2" s="64"/>
+      <c r="D2" s="63"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="63">
+      <c r="B3" s="62">
         <v>-5.4880659999999999</v>
       </c>
-      <c r="C3" s="63">
+      <c r="C3" s="62">
         <v>119.31312699999999</v>
       </c>
-      <c r="D3" s="64"/>
+      <c r="D3" s="63"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="63">
+      <c r="B4" s="62">
         <v>-5.4889159999999997</v>
       </c>
-      <c r="C4" s="63">
+      <c r="C4" s="62">
         <v>119.309448</v>
       </c>
-      <c r="D4" s="64"/>
+      <c r="D4" s="63"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="63">
+      <c r="B5" s="62">
         <v>-5.468826</v>
       </c>
-      <c r="C5" s="63">
+      <c r="C5" s="62">
         <v>119.300459</v>
       </c>
-      <c r="D5" s="64"/>
+      <c r="D5" s="63"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="63">
+      <c r="B6" s="62">
         <v>-5.4682649999999997</v>
       </c>
-      <c r="C6" s="63">
+      <c r="C6" s="62">
         <v>119.30207900000001</v>
       </c>
-      <c r="D6" s="64"/>
+      <c r="D6" s="63"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="62" t="s">
+      <c r="A7" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="63">
+      <c r="B7" s="62">
         <v>-5.4671349999999999</v>
       </c>
-      <c r="C7" s="63">
+      <c r="C7" s="62">
         <v>119.302812</v>
       </c>
-      <c r="D7" s="64"/>
+      <c r="D7" s="63"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="63">
+      <c r="B8" s="62">
         <v>-5.4901910000000003</v>
       </c>
-      <c r="C8" s="63">
+      <c r="C8" s="62">
         <v>119.311859</v>
       </c>
-      <c r="D8" s="64"/>
+      <c r="D8" s="63"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="63">
+      <c r="B9" s="62">
         <v>-5.491987</v>
       </c>
-      <c r="C9" s="63">
+      <c r="C9" s="62">
         <v>119.312573</v>
       </c>
-      <c r="D9" s="64"/>
+      <c r="D9" s="63"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="62" t="s">
+      <c r="A10" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="63">
+      <c r="B10" s="62">
         <v>-5.49282</v>
       </c>
-      <c r="C10" s="63">
+      <c r="C10" s="62">
         <v>119.31198000000001</v>
       </c>
-      <c r="D10" s="64"/>
+      <c r="D10" s="63"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="62" t="s">
+      <c r="A11" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="B11" s="63">
+      <c r="B11" s="62">
         <v>-5.4639509999999998</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="62">
         <v>119.287291</v>
       </c>
-      <c r="D11" s="64"/>
+      <c r="D11" s="63"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="B12" s="63">
+      <c r="B12" s="62">
         <v>-5.4620889999999997</v>
       </c>
-      <c r="C12" s="63">
+      <c r="C12" s="62">
         <v>119.286874</v>
       </c>
-      <c r="D12" s="64"/>
+      <c r="D12" s="63"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="63">
+      <c r="B13" s="62">
         <v>-5.463902</v>
       </c>
-      <c r="C13" s="63">
+      <c r="C13" s="62">
         <v>119.28802</v>
       </c>
-      <c r="D13" s="64"/>
+      <c r="D13" s="63"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="62" t="s">
+      <c r="A14" s="61" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="63">
+      <c r="B14" s="62">
         <v>-5.4810160000000003</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="62">
         <v>119.31128099999999</v>
       </c>
-      <c r="D14" s="64"/>
+      <c r="D14" s="63"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="61" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="63">
+      <c r="B15" s="62">
         <v>-5.4811319999999997</v>
       </c>
-      <c r="C15" s="63">
+      <c r="C15" s="62">
         <v>119.31211</v>
       </c>
-      <c r="D15" s="64"/>
+      <c r="D15" s="63"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="62" t="s">
+      <c r="A16" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="B16" s="63">
+      <c r="B16" s="62">
         <v>-5.4793599999999998</v>
       </c>
-      <c r="C16" s="63">
+      <c r="C16" s="62">
         <v>119.312033</v>
       </c>
-      <c r="D16" s="64"/>
+      <c r="D16" s="63"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="62" t="s">
+      <c r="A17" s="61" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="63">
+      <c r="B17" s="62">
         <v>-5.4663769999999996</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="62">
         <v>119.30229</v>
       </c>
-      <c r="D17" s="64"/>
+      <c r="D17" s="63"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="61" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="63">
+      <c r="B18" s="62">
         <v>-5.4682510000000004</v>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="62">
         <v>119.301957</v>
       </c>
-      <c r="D18" s="64"/>
+      <c r="D18" s="63"/>
     </row>
     <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="B19" s="66">
+      <c r="B19" s="65">
         <v>-5.4686510000000004</v>
       </c>
-      <c r="C19" s="66">
+      <c r="C19" s="65">
         <v>119.300428</v>
       </c>
-      <c r="D19" s="67"/>
+      <c r="D19" s="66"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/URUVS/Datasheets/URUV/05.2024/May_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/05.2024/May_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\05.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC2894B-121B-4353-8FFE-D12B5BC313EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2550C888-C8B5-467B-B4AA-6B093E802CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3840" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RecordingData_05.2024" sheetId="2" r:id="rId1"/>
@@ -2103,15 +2103,11 @@
       <c r="AK3" s="30">
         <v>3</v>
       </c>
-      <c r="AL3" s="31">
-        <v>44</v>
-      </c>
-      <c r="AM3" s="34">
-        <v>6.5046296296296302E-3</v>
-      </c>
-      <c r="AN3" s="33">
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="34"/>
+      <c r="AN3" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>2.0254629629629633E-3</v>
+        <v>NA</v>
       </c>
       <c r="AO3" s="31"/>
       <c r="AP3" s="32"/>
@@ -2160,14 +2156,13 @@
         <v>NA</v>
       </c>
       <c r="BJ3" s="31">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="BK3" s="34">
         <v>4.4212962962962956E-3</v>
       </c>
       <c r="BL3" s="33">
-        <f t="shared" si="9"/>
-        <v>-5.7870370370371321E-5</v>
+        <v>4.4791666666666669E-3</v>
       </c>
       <c r="BM3" s="31"/>
       <c r="BN3" s="32"/>
